--- a/database/event/4083/event_4083_evp_summary.xlsx
+++ b/database/event/4083/event_4083_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6015</v>
+        <v>6.1667</v>
       </c>
       <c r="C2" t="n">
-        <v>2.067</v>
+        <v>2.2756</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8415</v>
+        <v>2.0129</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6015</v>
+        <v>6.1667</v>
       </c>
       <c r="F2" t="n">
-        <v>2.964</v>
+        <v>3.5291</v>
       </c>
       <c r="G2" t="n">
         <v>2.6376</v>
       </c>
       <c r="H2" t="n">
-        <v>2.964</v>
+        <v>3.5291</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4024</v>
+        <v>2.8605</v>
       </c>
       <c r="J2" t="n">
         <v>2.6376</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>5.04</v>
+        <v>5.4981</v>
       </c>
       <c r="N2" t="n">
         <v>319</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7191</v>
+        <v>5.2241</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7414</v>
+        <v>1.9277</v>
       </c>
       <c r="D3" t="n">
-        <v>1.485</v>
+        <v>1.6374</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7191</v>
+        <v>5.2241</v>
       </c>
       <c r="F3" t="n">
-        <v>1.382</v>
+        <v>1.887</v>
       </c>
       <c r="G3" t="n">
         <v>3.3371</v>
       </c>
       <c r="H3" t="n">
-        <v>1.382</v>
+        <v>1.887</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1201</v>
+        <v>1.5295</v>
       </c>
       <c r="J3" t="n">
         <v>3.3371</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4572</v>
+        <v>4.8666</v>
       </c>
       <c r="N3" t="n">
         <v>319</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.131</v>
+        <v>4.381</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5244</v>
+        <v>1.6166</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2475</v>
+        <v>1.3015</v>
       </c>
       <c r="E4" t="n">
-        <v>4.131</v>
+        <v>4.381</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4003</v>
+        <v>1.6503</v>
       </c>
       <c r="G4" t="n">
         <v>2.7307</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4003</v>
+        <v>1.6503</v>
       </c>
       <c r="I4" t="n">
-        <v>1.135</v>
+        <v>1.3376</v>
       </c>
       <c r="J4" t="n">
         <v>2.7307</v>
@@ -621,7 +621,7 @@
         <v>139</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8657</v>
+        <v>4.0683</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7571</v>
+        <v>4.1087</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3864</v>
+        <v>1.5161</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0964</v>
+        <v>1.193</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7571</v>
+        <v>4.1087</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8737</v>
+        <v>4.2253</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1166</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8737</v>
+        <v>4.4388</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1397</v>
+        <v>3.5978</v>
       </c>
       <c r="J5" t="n">
         <v>-0.1166</v>
@@ -667,7 +667,7 @@
         <v>71</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0231</v>
+        <v>3.4812</v>
       </c>
       <c r="N5" t="n">
         <v>142</v>
@@ -676,185 +676,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5685</v>
+        <v>3.6111</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3168</v>
+        <v>1.3325</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0202</v>
+        <v>0.9948</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5685</v>
+        <v>3.6111</v>
       </c>
       <c r="F6" t="n">
-        <v>1.748</v>
+        <v>2.1703</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8205</v>
+        <v>1.4408</v>
       </c>
       <c r="H6" t="n">
-        <v>1.748</v>
+        <v>2.1703</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4168</v>
+        <v>1.7591</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8205</v>
+        <v>1.4408</v>
       </c>
       <c r="K6" t="n">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="L6" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2373</v>
+        <v>3.1999</v>
       </c>
       <c r="N6" t="n">
-        <v>260</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5178</v>
+        <v>3.5685</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2981</v>
+        <v>1.3168</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9998</v>
+        <v>0.9778</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5178</v>
+        <v>3.5685</v>
       </c>
       <c r="F7" t="n">
-        <v>2.077</v>
+        <v>1.748</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4408</v>
+        <v>1.8205</v>
       </c>
       <c r="H7" t="n">
-        <v>2.077</v>
+        <v>1.748</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6835</v>
+        <v>1.4168</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4408</v>
+        <v>1.8205</v>
       </c>
       <c r="K7" t="n">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="L7" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1243</v>
+        <v>3.2373</v>
       </c>
       <c r="N7" t="n">
-        <v>319</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.51</v>
+        <v>3.5351</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2952</v>
+        <v>1.3045</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9966</v>
+        <v>0.9645</v>
       </c>
       <c r="E8" t="n">
-        <v>3.51</v>
+        <v>3.5351</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7822</v>
+        <v>2.2535</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7278</v>
+        <v>1.2816</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7822</v>
+        <v>2.2535</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2551</v>
+        <v>1.8265</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7278</v>
+        <v>1.2816</v>
       </c>
       <c r="K8" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L8" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9829</v>
+        <v>3.1081</v>
       </c>
       <c r="N8" t="n">
-        <v>242</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3074</v>
+        <v>3.5222</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2205</v>
+        <v>1.2997</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9593</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3074</v>
+        <v>3.5222</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0258</v>
+        <v>2.7944</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2816</v>
+        <v>0.7278</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0258</v>
+        <v>2.7944</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6419</v>
+        <v>2.2649</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2816</v>
+        <v>0.7278</v>
       </c>
       <c r="K9" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L9" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9235</v>
+        <v>2.9927</v>
       </c>
       <c r="N9" t="n">
-        <v>319</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6478</v>
+        <v>2.6623</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9771</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6483</v>
+        <v>0.6168</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6478</v>
+        <v>2.6623</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1325</v>
+        <v>1.1469</v>
       </c>
       <c r="G10" t="n">
         <v>1.5154</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1325</v>
+        <v>1.1469</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9179</v>
+        <v>0.9296</v>
       </c>
       <c r="J10" t="n">
         <v>1.5154</v>
@@ -897,7 +897,7 @@
         <v>143</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4333</v>
+        <v>2.445</v>
       </c>
       <c r="N10" t="n">
         <v>319</v>
@@ -916,7 +916,7 @@
         <v>0.9227</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5888</v>
+        <v>0.5523</v>
       </c>
       <c r="E11" t="n">
         <v>2.5005</v>
@@ -952,277 +952,277 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9767</v>
+        <v>2.1304</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7294</v>
+        <v>0.7861</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3772</v>
+        <v>0.4048</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9767</v>
+        <v>2.1304</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9767</v>
+        <v>3.1933</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>-1.0629</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9767</v>
+        <v>3.1933</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4127</v>
+        <v>2.5883</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>-1.0629</v>
       </c>
       <c r="K12" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="L12" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4127</v>
+        <v>1.5254</v>
       </c>
       <c r="N12" t="n">
-        <v>142</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9758</v>
+        <v>1.9767</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7291</v>
+        <v>0.7294</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3768</v>
+        <v>0.3436</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9758</v>
+        <v>1.9767</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0387</v>
+        <v>2.9767</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0629</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0387</v>
+        <v>2.9767</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4629</v>
+        <v>2.4127</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0629</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="L13" t="n">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>1.4127</v>
       </c>
       <c r="N13" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7298</v>
+        <v>1.8933</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6383</v>
+        <v>0.6986</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2774</v>
+        <v>0.3104</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7298</v>
+        <v>1.8933</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7298</v>
+        <v>2.3878</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.4945</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7298</v>
+        <v>2.3878</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7298</v>
+        <v>1.9354</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.4945</v>
       </c>
       <c r="K14" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7298</v>
+        <v>1.4409</v>
       </c>
       <c r="N14" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4905</v>
+        <v>1.7298</v>
       </c>
       <c r="C15" t="n">
-        <v>0.55</v>
+        <v>0.6383</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1808</v>
+        <v>0.2452</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4905</v>
+        <v>1.7298</v>
       </c>
       <c r="F15" t="n">
-        <v>1.985</v>
+        <v>1.7298</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4945</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.985</v>
+        <v>1.7298</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6089</v>
+        <v>1.7298</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4945</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1144</v>
+        <v>1.7298</v>
       </c>
       <c r="N15" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2188</v>
+        <v>1.434</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4497</v>
+        <v>0.5292</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1274</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2188</v>
+        <v>1.434</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3944</v>
+        <v>2.0077</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6132</v>
+        <v>-0.5737</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3944</v>
+        <v>2.0077</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1302</v>
+        <v>1.6273</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6132</v>
+        <v>-0.5737</v>
       </c>
       <c r="K16" t="n">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="L16" t="n">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="M16" t="n">
-        <v>1.483</v>
+        <v>1.0536</v>
       </c>
       <c r="N16" t="n">
-        <v>260</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1278</v>
+        <v>1.2188</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4162</v>
+        <v>0.4497</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0342</v>
+        <v>0.0417</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1278</v>
+        <v>1.2188</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7015</v>
+        <v>-1.3944</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5737</v>
+        <v>2.6132</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7015</v>
+        <v>-1.3944</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3791</v>
+        <v>-1.1302</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5737</v>
+        <v>2.6132</v>
       </c>
       <c r="K17" t="n">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="L17" t="n">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8054</v>
+        <v>1.483</v>
       </c>
       <c r="N17" t="n">
-        <v>242</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1036</v>
+        <v>1.1895</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4072</v>
+        <v>0.4389</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0245</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1036</v>
+        <v>1.1895</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7006</v>
+        <v>1.7865</v>
       </c>
       <c r="G18" t="n">
         <v>-0.597</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7006</v>
+        <v>1.7865</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3784</v>
+        <v>1.448</v>
       </c>
       <c r="J18" t="n">
         <v>-0.597</v>
@@ -1265,7 +1265,7 @@
         <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7814000000000001</v>
+        <v>0.851</v>
       </c>
       <c r="N18" t="n">
         <v>142</v>
@@ -1284,7 +1284,7 @@
         <v>0.2476</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1503</v>
+        <v>-0.1765</v>
       </c>
       <c r="E19" t="n">
         <v>0.6711</v>
@@ -1330,7 +1330,7 @@
         <v>0.2399</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1587</v>
+        <v>-0.1849</v>
       </c>
       <c r="E20" t="n">
         <v>0.6501</v>
@@ -1376,7 +1376,7 @@
         <v>0.2134</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1878</v>
+        <v>-0.2136</v>
       </c>
       <c r="E21" t="n">
         <v>0.5782</v>
@@ -1422,7 +1422,7 @@
         <v>0.1769</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2277</v>
+        <v>-0.253</v>
       </c>
       <c r="E22" t="n">
         <v>0.4793</v>
@@ -1468,7 +1468,7 @@
         <v>0.0829</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3306</v>
+        <v>-0.3544</v>
       </c>
       <c r="E23" t="n">
         <v>0.2247</v>
@@ -1514,7 +1514,7 @@
         <v>0.0437</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3735</v>
+        <v>-0.3967</v>
       </c>
       <c r="E24" t="n">
         <v>0.1185</v>
@@ -1560,7 +1560,7 @@
         <v>0.0381</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3797</v>
+        <v>-0.4028</v>
       </c>
       <c r="E25" t="n">
         <v>0.1032</v>
@@ -1606,7 +1606,7 @@
         <v>0.0364</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3815</v>
+        <v>-0.4046</v>
       </c>
       <c r="E26" t="n">
         <v>0.0987</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0083</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4305</v>
+        <v>-0.4529</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0225</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0118</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4343</v>
+        <v>-0.4567</v>
       </c>
       <c r="E28" t="n">
         <v>-0.0321</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0479</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4738</v>
+        <v>-0.4956</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1297</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0873</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.517</v>
+        <v>-0.5382</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2367</v>
@@ -1836,7 +1836,7 @@
         <v>-0.123</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.556</v>
+        <v>-0.5767</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3333</v>
@@ -1882,7 +1882,7 @@
         <v>-0.359</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8144</v>
+        <v>-0.8316</v>
       </c>
       <c r="E32" t="n">
         <v>-0.973</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3594</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8148</v>
+        <v>-0.8319</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9739</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3662</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8223</v>
+        <v>-0.8393</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9923999999999999</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3754</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8324</v>
+        <v>-0.8492</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0174</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3914</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8499</v>
+        <v>-0.8665</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0607</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4381</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.901</v>
+        <v>-0.9169</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1873</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5581</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0323</v>
+        <v>-1.0464</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5123</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5668</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0419</v>
+        <v>-1.0559</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5361</v>
@@ -2250,7 +2250,7 @@
         <v>-0.716</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2052</v>
+        <v>-1.2169</v>
       </c>
       <c r="E40" t="n">
         <v>-1.9403</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1485</v>
+        <v>-2.0316</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.7497</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2893</v>
+        <v>-1.2533</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1485</v>
+        <v>-2.0316</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6566</v>
+        <v>-1.5397</v>
       </c>
       <c r="G41" t="n">
         <v>-0.4919</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6566</v>
+        <v>-1.5397</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3427</v>
+        <v>-1.248</v>
       </c>
       <c r="J41" t="n">
         <v>-0.4919</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8346</v>
+        <v>-1.7399</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>

--- a/database/event/4083/event_4083_evp_summary.xlsx
+++ b/database/event/4083/event_4083_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1667</v>
+        <v>5.4333</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2756</v>
+        <v>2.0049</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0129</v>
+        <v>1.8148</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1667</v>
+        <v>5.4333</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5291</v>
+        <v>3.094</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6376</v>
+        <v>2.3393</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5291</v>
+        <v>5.415</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8605</v>
+        <v>2.8156</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6376</v>
+        <v>2.3393</v>
       </c>
       <c r="K2" t="n">
         <v>176</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4981</v>
+        <v>5.1549</v>
       </c>
       <c r="N2" t="n">
         <v>319</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2241</v>
+        <v>5.178</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9277</v>
+        <v>1.9107</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6374</v>
+        <v>1.6996</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2241</v>
+        <v>5.178</v>
       </c>
       <c r="F3" t="n">
-        <v>1.887</v>
+        <v>2.4525</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3371</v>
+        <v>2.7255</v>
       </c>
       <c r="H3" t="n">
-        <v>1.887</v>
+        <v>3.1547</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5295</v>
+        <v>1.6403</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3371</v>
+        <v>2.7255</v>
       </c>
       <c r="K3" t="n">
         <v>176</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8666</v>
+        <v>4.3658</v>
       </c>
       <c r="N3" t="n">
         <v>319</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.381</v>
+        <v>4.8095</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6166</v>
+        <v>1.7747</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3015</v>
+        <v>1.5332</v>
       </c>
       <c r="E4" t="n">
-        <v>4.381</v>
+        <v>4.8095</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6503</v>
+        <v>2.3084</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7307</v>
+        <v>2.5011</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6503</v>
+        <v>2.6472</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3376</v>
+        <v>1.3764</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7307</v>
+        <v>2.5011</v>
       </c>
       <c r="K4" t="n">
         <v>121</v>
@@ -621,7 +621,7 @@
         <v>139</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0683</v>
+        <v>3.8775</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1087</v>
+        <v>4.3943</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5161</v>
+        <v>1.6215</v>
       </c>
       <c r="D5" t="n">
-        <v>1.193</v>
+        <v>1.3458</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1087</v>
+        <v>4.3943</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2253</v>
+        <v>2.4299</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1166</v>
+        <v>1.9644</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4388</v>
+        <v>3.0751</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5978</v>
+        <v>1.5989</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1166</v>
+        <v>1.9644</v>
       </c>
       <c r="K5" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="L5" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4812</v>
+        <v>3.5633</v>
       </c>
       <c r="N5" t="n">
-        <v>142</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6111</v>
+        <v>4.1274</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3325</v>
+        <v>1.523</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9948</v>
+        <v>1.2253</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6111</v>
+        <v>4.1274</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1703</v>
+        <v>2.6504</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4408</v>
+        <v>1.477</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1703</v>
+        <v>3.8519</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7591</v>
+        <v>2.0028</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4408</v>
+        <v>1.477</v>
       </c>
       <c r="K6" t="n">
         <v>176</v>
@@ -713,7 +713,7 @@
         <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1999</v>
+        <v>3.4798</v>
       </c>
       <c r="N6" t="n">
         <v>319</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5685</v>
+        <v>4.033</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3168</v>
+        <v>1.4882</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9778</v>
+        <v>1.1827</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5685</v>
+        <v>4.033</v>
       </c>
       <c r="F7" t="n">
-        <v>1.748</v>
+        <v>2.7257</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8205</v>
+        <v>1.3073</v>
       </c>
       <c r="H7" t="n">
-        <v>1.748</v>
+        <v>4.1173</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4168</v>
+        <v>2.1408</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8205</v>
+        <v>1.3073</v>
       </c>
       <c r="K7" t="n">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="L7" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2373</v>
+        <v>3.4481</v>
       </c>
       <c r="N7" t="n">
-        <v>260</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5351</v>
+        <v>3.6679</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3045</v>
+        <v>1.3535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9645</v>
+        <v>1.0179</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5351</v>
+        <v>3.6679</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2535</v>
+        <v>2.8992</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2816</v>
+        <v>0.7687</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2535</v>
+        <v>4.7287</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8265</v>
+        <v>2.4587</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2816</v>
+        <v>0.7687</v>
       </c>
       <c r="K8" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L8" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1081</v>
+        <v>3.2274</v>
       </c>
       <c r="N8" t="n">
-        <v>319</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5222</v>
+        <v>3.3362</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2997</v>
+        <v>1.2311</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9593</v>
+        <v>0.8681</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5222</v>
+        <v>3.3362</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7944</v>
+        <v>2.251</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7278</v>
+        <v>1.0852</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7944</v>
+        <v>2.4448</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2649</v>
+        <v>1.2712</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7278</v>
+        <v>1.0852</v>
       </c>
       <c r="K9" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L9" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9927</v>
+        <v>2.3564</v>
       </c>
       <c r="N9" t="n">
-        <v>242</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6623</v>
+        <v>3.2877</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.2132</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6168</v>
+        <v>0.8462</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6623</v>
+        <v>3.2877</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1469</v>
+        <v>3.3851</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5154</v>
+        <v>-0.0974</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1469</v>
+        <v>6.4406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9296</v>
+        <v>3.3488</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5154</v>
+        <v>-0.0974</v>
       </c>
       <c r="K10" t="n">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="L10" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>2.445</v>
+        <v>3.2514</v>
       </c>
       <c r="N10" t="n">
-        <v>319</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5005</v>
+        <v>2.6974</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9227</v>
+        <v>0.9954</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5523</v>
+        <v>0.5797</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5005</v>
+        <v>2.6974</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5005</v>
+        <v>2.6974</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5005</v>
+        <v>2.6974</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5005</v>
+        <v>2.6974</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5005</v>
+        <v>2.6974</v>
       </c>
       <c r="N11" t="n">
         <v>173</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1304</v>
+        <v>2.687</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7861</v>
+        <v>0.9915</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4048</v>
+        <v>0.575</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1304</v>
+        <v>2.687</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1933</v>
+        <v>2.687</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0629</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1933</v>
+        <v>2.687</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5883</v>
+        <v>2.687</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0629</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L12" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5254</v>
+        <v>2.687</v>
       </c>
       <c r="N12" t="n">
-        <v>260</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9767</v>
+        <v>2.3923</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7294</v>
+        <v>0.8828</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3436</v>
+        <v>0.442</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9767</v>
+        <v>2.3923</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9767</v>
+        <v>2.9364</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>-0.5441</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9767</v>
+        <v>4.8599</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4127</v>
+        <v>2.5269</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>-0.5441</v>
       </c>
       <c r="K13" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="L13" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4127</v>
+        <v>1.9828</v>
       </c>
       <c r="N13" t="n">
-        <v>142</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8933</v>
+        <v>2.3061</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6986</v>
+        <v>0.851</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3104</v>
+        <v>0.4031</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8933</v>
+        <v>2.3061</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3878</v>
+        <v>2.6053</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4945</v>
+        <v>-0.2992</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3878</v>
+        <v>3.6932</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9354</v>
+        <v>1.9203</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4945</v>
+        <v>-0.2992</v>
       </c>
       <c r="K14" t="n">
         <v>71</v>
@@ -1081,7 +1081,7 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4409</v>
+        <v>1.6211</v>
       </c>
       <c r="N14" t="n">
         <v>142</v>
@@ -1090,323 +1090,323 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7298</v>
+        <v>2.1109</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6383</v>
+        <v>0.7789</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2452</v>
+        <v>0.315</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7298</v>
+        <v>2.1109</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7298</v>
+        <v>2.4356</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.3247</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7298</v>
+        <v>3.0951</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7298</v>
+        <v>1.6093</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.3247</v>
       </c>
       <c r="K15" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7298</v>
+        <v>1.2846</v>
       </c>
       <c r="N15" t="n">
-        <v>135</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.434</v>
+        <v>2.0749</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5292</v>
+        <v>0.7657</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1274</v>
+        <v>0.2987</v>
       </c>
       <c r="E16" t="n">
-        <v>1.434</v>
+        <v>2.0749</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0077</v>
+        <v>2.475</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5737</v>
+        <v>-0.4001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0077</v>
+        <v>3.2341</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6273</v>
+        <v>1.6816</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5737</v>
+        <v>-0.4001</v>
       </c>
       <c r="K16" t="n">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="L16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0536</v>
+        <v>1.2815</v>
       </c>
       <c r="N16" t="n">
-        <v>242</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2188</v>
+        <v>2.0439</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4497</v>
+        <v>0.7542</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0417</v>
+        <v>0.2847</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2188</v>
+        <v>2.0439</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3944</v>
+        <v>3.0439</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6132</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3944</v>
+        <v>5.2385</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1302</v>
+        <v>2.7238</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6132</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="L17" t="n">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="M17" t="n">
-        <v>1.483</v>
+        <v>1.7238</v>
       </c>
       <c r="N17" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1895</v>
+        <v>1.5986</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4389</v>
+        <v>0.5899</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>0.0837</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1895</v>
+        <v>1.5986</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7865</v>
+        <v>1.5986</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.597</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7865</v>
+        <v>1.5986</v>
       </c>
       <c r="I18" t="n">
-        <v>1.448</v>
+        <v>1.5986</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.597</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="L18" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.851</v>
+        <v>1.5986</v>
       </c>
       <c r="N18" t="n">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6711</v>
+        <v>1.3124</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2476</v>
+        <v>0.4843</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1765</v>
+        <v>-0.0455</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6711</v>
+        <v>1.3124</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6711</v>
+        <v>0.7941</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.5183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6711</v>
+        <v>0.7941</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6711</v>
+        <v>0.4129</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.5183</v>
       </c>
       <c r="K19" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6711</v>
+        <v>0.9312</v>
       </c>
       <c r="N19" t="n">
-        <v>135</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6501</v>
+        <v>0.8515</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2399</v>
+        <v>0.3142</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1849</v>
+        <v>-0.2536</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6501</v>
+        <v>0.8515</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0007</v>
+        <v>0.8515</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6508</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0007</v>
+        <v>0.8515</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.8515</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6508</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="L20" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6502</v>
+        <v>0.8515</v>
       </c>
       <c r="N20" t="n">
-        <v>242</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5782</v>
+        <v>0.7356</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2134</v>
+        <v>0.2714</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2136</v>
+        <v>-0.3059</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5782</v>
+        <v>0.7356</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5782</v>
+        <v>-1.4701</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.2058</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5782</v>
+        <v>-1.4701</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5782</v>
+        <v>-0.7644</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.2058</v>
       </c>
       <c r="K21" t="n">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5782</v>
+        <v>1.4414</v>
       </c>
       <c r="N21" t="n">
-        <v>173</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4793</v>
+        <v>0.6253</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1769</v>
+        <v>0.2307</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.253</v>
+        <v>-0.3557</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4793</v>
+        <v>0.6253</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4793</v>
+        <v>0.6253</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4793</v>
+        <v>0.6253</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4793</v>
+        <v>0.6253</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4793</v>
+        <v>0.6253</v>
       </c>
       <c r="N22" t="n">
         <v>72</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2247</v>
+        <v>0.5802</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0829</v>
+        <v>0.2141</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3544</v>
+        <v>-0.3761</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2247</v>
+        <v>0.5802</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2247</v>
+        <v>0.7741</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.1939</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2247</v>
+        <v>0.7741</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2247</v>
+        <v>0.4025</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.1939</v>
       </c>
       <c r="K23" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2247</v>
+        <v>0.2086</v>
       </c>
       <c r="N23" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1185</v>
+        <v>0.4618</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0437</v>
+        <v>0.1704</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3967</v>
+        <v>-0.4295</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1185</v>
+        <v>0.4618</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1185</v>
+        <v>0.4618</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1185</v>
+        <v>0.4618</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1185</v>
+        <v>0.4618</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1185</v>
+        <v>0.4618</v>
       </c>
       <c r="N24" t="n">
         <v>173</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1032</v>
+        <v>0.4331</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0381</v>
+        <v>0.1598</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4028</v>
+        <v>-0.4425</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1032</v>
+        <v>0.4331</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1032</v>
+        <v>0.4331</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1032</v>
+        <v>0.4331</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1032</v>
+        <v>0.4331</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1032</v>
+        <v>0.4331</v>
       </c>
       <c r="N25" t="n">
         <v>135</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0987</v>
+        <v>0.342</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0364</v>
+        <v>0.1262</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4046</v>
+        <v>-0.4836</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0987</v>
+        <v>0.342</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0987</v>
+        <v>0.342</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0987</v>
+        <v>0.342</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0987</v>
+        <v>0.342</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0987</v>
+        <v>0.342</v>
       </c>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0225</v>
+        <v>0.2953</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0083</v>
+        <v>0.109</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4529</v>
+        <v>-0.5047</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0225</v>
+        <v>0.2953</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0225</v>
+        <v>0.2953</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0225</v>
+        <v>0.2953</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0225</v>
+        <v>0.2953</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0225</v>
+        <v>0.2953</v>
       </c>
       <c r="N27" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0321</v>
+        <v>0.2468</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0118</v>
+        <v>0.0911</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4567</v>
+        <v>-0.5266</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0321</v>
+        <v>0.2468</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1976</v>
+        <v>0.2468</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2297</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1976</v>
+        <v>0.2468</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1602</v>
+        <v>0.2468</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2297</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L28" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.06949999999999998</v>
+        <v>0.2468</v>
       </c>
       <c r="N28" t="n">
-        <v>142</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1297</v>
+        <v>0.0717</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0479</v>
+        <v>0.0265</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4956</v>
+        <v>-0.6056</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1297</v>
+        <v>0.0717</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1297</v>
+        <v>0.0717</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1297</v>
+        <v>0.0717</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1297</v>
+        <v>0.0717</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1297</v>
+        <v>0.0717</v>
       </c>
       <c r="N29" t="n">
         <v>173</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2367</v>
+        <v>0.047</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0873</v>
+        <v>0.0173</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5382</v>
+        <v>-0.6168</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2367</v>
+        <v>0.047</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2367</v>
+        <v>0.047</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2367</v>
+        <v>0.047</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2367</v>
+        <v>0.047</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2367</v>
+        <v>0.047</v>
       </c>
       <c r="N30" t="n">
         <v>72</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1618</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.123</v>
+        <v>-0.0597</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5767</v>
+        <v>-0.7111</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1618</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1618</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1618</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1618</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3333</v>
+        <v>-0.1618</v>
       </c>
       <c r="N31" t="n">
         <v>81</v>
@@ -1872,216 +1872,216 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.973</v>
+        <v>-0.4154</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.359</v>
+        <v>-0.1533</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8316</v>
+        <v>-0.8255</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.973</v>
+        <v>-0.4154</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.973</v>
+        <v>0.3183</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.7337</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.973</v>
+        <v>0.3183</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.973</v>
+        <v>0.1655</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.7337</v>
       </c>
       <c r="K32" t="n">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.973</v>
+        <v>-0.5682</v>
       </c>
       <c r="N32" t="n">
-        <v>81</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9739</v>
+        <v>-0.5743</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3594</v>
+        <v>-0.2119</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8319</v>
+        <v>-0.8973</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9739</v>
+        <v>-0.5743</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9739</v>
+        <v>-0.5743</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9739</v>
+        <v>-0.5743</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9739</v>
+        <v>-0.5743</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9739</v>
+        <v>-0.5743</v>
       </c>
       <c r="N33" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6007</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3662</v>
+        <v>-0.2217</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8393</v>
+        <v>-0.9092</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6007</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6007</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6007</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6007</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6007</v>
       </c>
       <c r="N34" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0174</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3754</v>
+        <v>-0.2442</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8492</v>
+        <v>-0.9368</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0174</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0174</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0174</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0174</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0174</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0607</v>
+        <v>-0.7417</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3914</v>
+        <v>-0.2737</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8665</v>
+        <v>-0.9729</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0607</v>
+        <v>-0.7417</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0607</v>
+        <v>-0.7417</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0607</v>
+        <v>-0.7417</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0607</v>
+        <v>-0.7417</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0607</v>
+        <v>-0.7417</v>
       </c>
       <c r="N36" t="n">
         <v>72</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1873</v>
+        <v>-0.7421</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4381</v>
+        <v>-0.2738</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9169</v>
+        <v>-0.973</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1873</v>
+        <v>-0.7421</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1873</v>
+        <v>-0.7421</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1873</v>
+        <v>-0.7421</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1518</v>
+        <v>-0.7421</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="L37" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1518</v>
+        <v>-0.7421</v>
       </c>
       <c r="N37" t="n">
-        <v>242</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5123</v>
+        <v>-1.0282</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5581</v>
+        <v>-0.3794</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0464</v>
+        <v>-1.1022</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5123</v>
+        <v>-1.0282</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.232</v>
+        <v>-0.9749</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2803</v>
+        <v>-0.0533</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.232</v>
+        <v>-0.9749</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9986</v>
+        <v>-0.5069</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2803</v>
+        <v>-0.0533</v>
       </c>
       <c r="K38" t="n">
         <v>175</v>
@@ -2185,7 +2185,7 @@
         <v>67</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2789</v>
+        <v>-0.5602</v>
       </c>
       <c r="N38" t="n">
         <v>242</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5361</v>
+        <v>-1.0751</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5668</v>
+        <v>-0.3967</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0559</v>
+        <v>-1.1234</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5361</v>
+        <v>-1.0751</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5361</v>
+        <v>-1.0751</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5361</v>
+        <v>-1.0751</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5361</v>
+        <v>-1.0751</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5361</v>
+        <v>-1.0751</v>
       </c>
       <c r="N39" t="n">
         <v>173</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9403</v>
+        <v>-1.614</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.716</v>
+        <v>-0.5956</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2169</v>
+        <v>-1.3667</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9403</v>
+        <v>-1.614</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9403</v>
+        <v>-1.614</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9403</v>
+        <v>-1.614</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9403</v>
+        <v>-1.614</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9403</v>
+        <v>-1.614</v>
       </c>
       <c r="N40" t="n">
         <v>72</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0316</v>
+        <v>-2.2107</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7497</v>
+        <v>-0.8158</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2533</v>
+        <v>-1.636</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0316</v>
+        <v>-2.2107</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5397</v>
+        <v>-1.8682</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4919</v>
+        <v>-0.3425</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5397</v>
+        <v>-1.8682</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.248</v>
+        <v>-0.9714</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4919</v>
+        <v>-0.3425</v>
       </c>
       <c r="K41" t="n">
         <v>121</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7399</v>
+        <v>-1.3139</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4029</v>
+        <v>0.3661</v>
       </c>
       <c r="J2" t="n">
-        <v>12.087</v>
+        <v>10.983</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3729</v>
+        <v>0.3378</v>
       </c>
       <c r="J3" t="n">
-        <v>11.187</v>
+        <v>10.134</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0713</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.139</v>
+        <v>2.637</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0384</v>
+        <v>-0.0065</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.152</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2908</v>
+        <v>-0.2383</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.724</v>
+        <v>-7.149</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7927</v>
+        <v>0.9849</v>
       </c>
       <c r="J7" t="n">
-        <v>23.781</v>
+        <v>29.547</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="J8" t="n">
-        <v>1.881</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.076</v>
+        <v>-0.0285</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.28</v>
+        <v>-0.855</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1437</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.311</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2673</v>
+        <v>-0.1547</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.019</v>
+        <v>-4.641</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6762</v>
       </c>
       <c r="J12" t="n">
-        <v>29.2362</v>
+        <v>28.4004</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6464</v>
+        <v>0.6272</v>
       </c>
       <c r="J13" t="n">
-        <v>27.1488</v>
+        <v>26.3424</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4283</v>
+        <v>0.4254</v>
       </c>
       <c r="J14" t="n">
-        <v>17.9886</v>
+        <v>17.8668</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2233</v>
+        <v>0.2639</v>
       </c>
       <c r="J15" t="n">
-        <v>9.3786</v>
+        <v>11.0838</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4206</v>
+        <v>-0.3529</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.6652</v>
+        <v>-14.8218</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4978</v>
+        <v>0.5936</v>
       </c>
       <c r="J17" t="n">
-        <v>20.9076</v>
+        <v>24.9312</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1808</v>
+        <v>0.2124</v>
       </c>
       <c r="J18" t="n">
-        <v>7.5936</v>
+        <v>8.9208</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1611</v>
+        <v>0.1923</v>
       </c>
       <c r="J19" t="n">
-        <v>6.7662</v>
+        <v>8.076599999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0702</v>
+        <v>-0.0267</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9484</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2791</v>
+        <v>-0.1637</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.7222</v>
+        <v>-6.8754</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.25</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0816</v>
+        <v>1.6514</v>
       </c>
       <c r="J22" t="n">
-        <v>37.4688</v>
+        <v>29.7252</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.67</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3942</v>
+        <v>1.0108</v>
       </c>
       <c r="J23" t="n">
-        <v>25.0956</v>
+        <v>18.1944</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.52</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0667</v>
+        <v>0.8404</v>
       </c>
       <c r="J24" t="n">
-        <v>19.2006</v>
+        <v>15.1272</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.23</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4436</v>
+        <v>0.4693</v>
       </c>
       <c r="J25" t="n">
-        <v>7.9848</v>
+        <v>8.4474</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0134</v>
+        <v>0.0771</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2412</v>
+        <v>1.3878</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2582</v>
+        <v>0.2702</v>
       </c>
       <c r="J27" t="n">
-        <v>4.6476</v>
+        <v>4.8636</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.66</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.423</v>
+        <v>-0.3242</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.614</v>
+        <v>-5.8356</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.6</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5402</v>
+        <v>-0.3774</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.723599999999999</v>
+        <v>-6.7932</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.49</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7032</v>
+        <v>-0.4797</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.6576</v>
+        <v>-8.634600000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.36</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8723</v>
+        <v>-0.603</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.7014</v>
+        <v>-10.854</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3911</v>
+        <v>0.331</v>
       </c>
       <c r="J32" t="n">
-        <v>9.3864</v>
+        <v>7.944</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2113</v>
+        <v>0.1561</v>
       </c>
       <c r="J33" t="n">
-        <v>5.0712</v>
+        <v>3.7464</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3078</v>
+        <v>-0.2021</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.3872</v>
+        <v>-4.8504</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4464</v>
+        <v>-0.2901</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.7136</v>
+        <v>-6.9624</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.52</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7209</v>
+        <v>-0.4867</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.3016</v>
+        <v>-11.6808</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9565</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>22.956</v>
+        <v>15.6648</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4097</v>
+        <v>0.3662</v>
       </c>
       <c r="J38" t="n">
-        <v>9.832800000000001</v>
+        <v>8.7888</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.2</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2616</v>
+        <v>0.2721</v>
       </c>
       <c r="J39" t="n">
-        <v>6.2784</v>
+        <v>6.5304</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2181</v>
+        <v>0.2344</v>
       </c>
       <c r="J40" t="n">
-        <v>5.2344</v>
+        <v>5.6256</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.08</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0789</v>
+        <v>0.1109</v>
       </c>
       <c r="J41" t="n">
-        <v>1.8936</v>
+        <v>2.6616</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7302</v>
+        <v>0.548</v>
       </c>
       <c r="J42" t="n">
-        <v>18.255</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6312</v>
+        <v>0.4887</v>
       </c>
       <c r="J43" t="n">
-        <v>15.78</v>
+        <v>12.2175</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.13</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4431</v>
+        <v>0.3808</v>
       </c>
       <c r="J44" t="n">
-        <v>11.0775</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0567</v>
+        <v>-0.0127</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.4175</v>
+        <v>-0.3175</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8551</v>
+        <v>-0.8165</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.3775</v>
+        <v>-20.4125</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2515</v>
+        <v>0.2641</v>
       </c>
       <c r="J47" t="n">
-        <v>6.2875</v>
+        <v>6.6025</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2345</v>
+        <v>0.243</v>
       </c>
       <c r="J48" t="n">
-        <v>5.8625</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1613</v>
+        <v>0.1543</v>
       </c>
       <c r="J49" t="n">
-        <v>4.0325</v>
+        <v>3.8575</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.79</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3824</v>
+        <v>-0.2416</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.56</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.66</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5604</v>
+        <v>-0.3667</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.01</v>
+        <v>-9.1675</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.93</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0623</v>
+        <v>-0.0735</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.4329</v>
+        <v>-1.6905</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0857</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.8561</v>
+        <v>-1.9711</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.255</v>
+        <v>-0.1953</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.865</v>
+        <v>-4.4919</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4951</v>
+        <v>-0.328</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.3873</v>
+        <v>-7.544</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.6</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6051</v>
+        <v>-0.4033</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.9173</v>
+        <v>-9.2759</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.57</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3049</v>
+        <v>0.9296</v>
       </c>
       <c r="J57" t="n">
-        <v>30.0127</v>
+        <v>21.3808</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.43</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0197</v>
+        <v>0.756</v>
       </c>
       <c r="J58" t="n">
-        <v>23.4531</v>
+        <v>17.388</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.37</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8859</v>
+        <v>0.6801</v>
       </c>
       <c r="J59" t="n">
-        <v>20.3757</v>
+        <v>15.6423</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2965</v>
+        <v>0.3641</v>
       </c>
       <c r="J60" t="n">
-        <v>6.8195</v>
+        <v>8.3743</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1033</v>
+        <v>0.1873</v>
       </c>
       <c r="J61" t="n">
-        <v>2.3759</v>
+        <v>4.3079</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4069</v>
+        <v>0.3378</v>
       </c>
       <c r="J62" t="n">
-        <v>10.9863</v>
+        <v>9.1206</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3344</v>
+        <v>0.2809</v>
       </c>
       <c r="J63" t="n">
-        <v>9.0288</v>
+        <v>7.5843</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2555</v>
+        <v>0.2162</v>
       </c>
       <c r="J64" t="n">
-        <v>6.8985</v>
+        <v>5.8374</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0984</v>
+        <v>0.1048</v>
       </c>
       <c r="J65" t="n">
-        <v>2.6568</v>
+        <v>2.8296</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3165</v>
+        <v>-0.1883</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.545500000000001</v>
+        <v>-5.0841</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5825</v>
+        <v>0.4527</v>
       </c>
       <c r="J67" t="n">
-        <v>15.7275</v>
+        <v>12.2229</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.058</v>
+        <v>0.033</v>
       </c>
       <c r="J68" t="n">
-        <v>1.566</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1614</v>
+        <v>-0.0968</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.3578</v>
+        <v>-2.6136</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.8563</v>
+        <v>-3.5289</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5661</v>
+        <v>-0.3703</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.2847</v>
+        <v>-9.998100000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.77</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.2474</v>
+        <v>-0.213</v>
       </c>
       <c r="J72" t="n">
-        <v>-5.1954</v>
+        <v>-4.473</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.77</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2474</v>
+        <v>-0.213</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.1954</v>
+        <v>-4.473</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3887</v>
+        <v>-0.3048</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.162699999999999</v>
+        <v>-6.4008</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.53</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6464</v>
+        <v>-0.4417</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.5744</v>
+        <v>-9.275700000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.38</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8468</v>
+        <v>-0.5836</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.7828</v>
+        <v>-12.2556</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.91</v>
       </c>
       <c r="I77" t="n">
-        <v>1.7874</v>
+        <v>1.2883</v>
       </c>
       <c r="J77" t="n">
-        <v>37.5354</v>
+        <v>27.0543</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.63</v>
       </c>
       <c r="I78" t="n">
-        <v>1.3353</v>
+        <v>0.9701</v>
       </c>
       <c r="J78" t="n">
-        <v>28.0413</v>
+        <v>20.3721</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.55</v>
       </c>
       <c r="I79" t="n">
-        <v>1.173</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>24.633</v>
+        <v>18.4275</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6977</v>
+        <v>0.6233</v>
       </c>
       <c r="J80" t="n">
-        <v>14.6517</v>
+        <v>13.0893</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.09</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1103</v>
+        <v>0.2065</v>
       </c>
       <c r="J81" t="n">
-        <v>2.3163</v>
+        <v>4.3365</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6942</v>
+        <v>1.4558</v>
       </c>
       <c r="J82" t="n">
-        <v>50.826</v>
+        <v>43.674</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.04</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1037</v>
+        <v>0.1453</v>
       </c>
       <c r="J83" t="n">
-        <v>3.111</v>
+        <v>4.359</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0271</v>
+        <v>0.0741</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8129999999999999</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.89</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4682</v>
+        <v>-0.4044</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.046</v>
+        <v>-12.132</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7008</v>
+        <v>-0.6481</v>
       </c>
       <c r="J86" t="n">
-        <v>-21.024</v>
+        <v>-19.443</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.47</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7064</v>
+        <v>0.8733</v>
       </c>
       <c r="J87" t="n">
-        <v>21.192</v>
+        <v>26.199</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.17</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3144</v>
+        <v>0.3645</v>
       </c>
       <c r="J88" t="n">
-        <v>9.432</v>
+        <v>10.935</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0362</v>
+        <v>-0.0059</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.086</v>
+        <v>-0.177</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.88</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2796</v>
+        <v>-0.1639</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.388</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.83</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3554</v>
+        <v>-0.2165</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.662</v>
+        <v>-6.495</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3281</v>
+        <v>0.2861</v>
       </c>
       <c r="J92" t="n">
-        <v>13.4521</v>
+        <v>11.7301</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1975</v>
+        <v>0.1674</v>
       </c>
       <c r="J93" t="n">
-        <v>8.0975</v>
+        <v>6.8634</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0149</v>
+        <v>0.026</v>
       </c>
       <c r="J94" t="n">
-        <v>0.6109</v>
+        <v>1.066</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.01</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0149</v>
+        <v>0.026</v>
       </c>
       <c r="J95" t="n">
-        <v>0.6109</v>
+        <v>1.066</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2702</v>
+        <v>-0.1597</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.0782</v>
+        <v>-6.5477</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.27</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4475</v>
+        <v>0.3798</v>
       </c>
       <c r="J97" t="n">
-        <v>18.3475</v>
+        <v>15.5718</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2712</v>
+        <v>0.2291</v>
       </c>
       <c r="J98" t="n">
-        <v>11.1192</v>
+        <v>9.3931</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2375</v>
+        <v>0.2027</v>
       </c>
       <c r="J99" t="n">
-        <v>9.737500000000001</v>
+        <v>8.310700000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.02</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0136</v>
+        <v>0.0365</v>
       </c>
       <c r="J100" t="n">
-        <v>0.5576</v>
+        <v>1.4965</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.93</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2035</v>
+        <v>-0.1107</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.343500000000001</v>
+        <v>-4.5387</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7625</v>
+        <v>0.7817</v>
       </c>
       <c r="J102" t="n">
-        <v>20.5875</v>
+        <v>21.1059</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.29</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7378</v>
+        <v>0.7591</v>
       </c>
       <c r="J103" t="n">
-        <v>19.9206</v>
+        <v>20.4957</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.28</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7125</v>
+        <v>0.7365</v>
       </c>
       <c r="J104" t="n">
-        <v>19.2375</v>
+        <v>19.8855</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6286</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>16.9722</v>
+        <v>18.0603</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2704</v>
+        <v>0.3468</v>
       </c>
       <c r="J106" t="n">
-        <v>7.3008</v>
+        <v>9.3636</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2426</v>
+        <v>0.2447</v>
       </c>
       <c r="J107" t="n">
-        <v>6.5502</v>
+        <v>6.6069</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0182</v>
+        <v>-0.0363</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.4914</v>
+        <v>-0.9801</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2215</v>
+        <v>-0.1532</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.9805</v>
+        <v>-4.1364</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2215</v>
+        <v>-0.1532</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.9805</v>
+        <v>-4.1364</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6617</v>
+        <v>-0.4422</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.8659</v>
+        <v>-11.9394</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0955</v>
+        <v>1.0525</v>
       </c>
       <c r="J112" t="n">
-        <v>32.865</v>
+        <v>31.575</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.17</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5353</v>
+        <v>0.5105</v>
       </c>
       <c r="J113" t="n">
-        <v>16.059</v>
+        <v>15.315</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5081</v>
+        <v>0.4847</v>
       </c>
       <c r="J114" t="n">
-        <v>15.243</v>
+        <v>14.541</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3489</v>
+        <v>-0.2844</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.467</v>
+        <v>-8.532</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.77</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7706</v>
+        <v>-0.7236</v>
       </c>
       <c r="J116" t="n">
-        <v>-23.118</v>
+        <v>-21.708</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.22</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4232</v>
+        <v>0.4865</v>
       </c>
       <c r="J117" t="n">
-        <v>12.696</v>
+        <v>14.595</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.13</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2893</v>
+        <v>0.3155</v>
       </c>
       <c r="J118" t="n">
-        <v>8.679</v>
+        <v>9.465</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.96</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0973</v>
+        <v>-0.0605</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.919</v>
+        <v>-1.815</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4047</v>
+        <v>-0.2551</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.141</v>
+        <v>-7.653</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4468</v>
+        <v>-0.2845</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.404</v>
+        <v>-8.535</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.31</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8789</v>
+        <v>0.8567</v>
       </c>
       <c r="J122" t="n">
-        <v>25.4881</v>
+        <v>24.8443</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6905</v>
+        <v>0.6625</v>
       </c>
       <c r="J123" t="n">
-        <v>20.0245</v>
+        <v>19.2125</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3633</v>
+        <v>0.3524</v>
       </c>
       <c r="J124" t="n">
-        <v>10.5357</v>
+        <v>10.2196</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1805</v>
+        <v>0.211</v>
       </c>
       <c r="J125" t="n">
-        <v>5.2345</v>
+        <v>6.119</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.885</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-25.665</v>
+        <v>-24.6007</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2696</v>
+        <v>0.2927</v>
       </c>
       <c r="J127" t="n">
-        <v>7.8184</v>
+        <v>8.488300000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1645</v>
+        <v>0.1667</v>
       </c>
       <c r="J128" t="n">
-        <v>4.7705</v>
+        <v>4.8343</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2028</v>
+        <v>-0.1207</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.8812</v>
+        <v>-3.5003</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2205</v>
+        <v>-0.1318</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.3945</v>
+        <v>-3.8222</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2205</v>
+        <v>-0.1318</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.3945</v>
+        <v>-3.8222</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.41</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0513</v>
+        <v>1.0286</v>
       </c>
       <c r="J132" t="n">
-        <v>31.539</v>
+        <v>30.858</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9215</v>
+        <v>0.9163</v>
       </c>
       <c r="J133" t="n">
-        <v>27.645</v>
+        <v>27.489</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3682</v>
+        <v>0.4169</v>
       </c>
       <c r="J134" t="n">
-        <v>11.046</v>
+        <v>12.507</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0537</v>
+        <v>0.0134</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.611</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3189</v>
+        <v>-0.2433</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.567</v>
+        <v>-7.299</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>0.397</v>
+        <v>0.4483</v>
       </c>
       <c r="J137" t="n">
-        <v>11.91</v>
+        <v>13.449</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2053</v>
+        <v>0.2047</v>
       </c>
       <c r="J138" t="n">
-        <v>6.159</v>
+        <v>6.141</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1061</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.183</v>
+        <v>-2.448</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3628</v>
+        <v>-0.2296</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.884</v>
+        <v>-6.888</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.621</v>
+        <v>-0.4114</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.63</v>
+        <v>-12.342</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6739</v>
+        <v>1.4408</v>
       </c>
       <c r="J142" t="n">
-        <v>38.4997</v>
+        <v>33.1384</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.42</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0366</v>
+        <v>1.0268</v>
       </c>
       <c r="J143" t="n">
-        <v>23.8418</v>
+        <v>23.6164</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0152</v>
+        <v>1.0113</v>
       </c>
       <c r="J144" t="n">
-        <v>23.3496</v>
+        <v>23.2599</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6435</v>
+        <v>-0.58</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.8005</v>
+        <v>-13.34</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.763</v>
+        <v>-0.7105</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.549</v>
+        <v>-16.3415</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.03</v>
       </c>
       <c r="I147" t="n">
-        <v>0.174</v>
+        <v>0.1525</v>
       </c>
       <c r="J147" t="n">
-        <v>4.002</v>
+        <v>3.5075</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1592</v>
+        <v>-0.1348</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.6616</v>
+        <v>-3.1004</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.87</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1767</v>
+        <v>-0.1457</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.0641</v>
+        <v>-3.3511</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3806</v>
+        <v>-0.2541</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.7538</v>
+        <v>-5.8443</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7479</v>
+        <v>-0.5074</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.2017</v>
+        <v>-11.6702</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5639</v>
+        <v>0.6798</v>
       </c>
       <c r="J152" t="n">
-        <v>16.917</v>
+        <v>20.394</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.34</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5513</v>
+        <v>0.6631</v>
       </c>
       <c r="J153" t="n">
-        <v>16.539</v>
+        <v>19.893</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0333</v>
+        <v>-0.0051</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.999</v>
+        <v>-0.153</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2934</v>
+        <v>-0.1738</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.802</v>
+        <v>-5.214</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4653</v>
+        <v>-0.2952</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.959</v>
+        <v>-8.856</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.46</v>
       </c>
       <c r="I157" t="n">
-        <v>1.247</v>
+        <v>1.1505</v>
       </c>
       <c r="J157" t="n">
-        <v>37.41</v>
+        <v>34.515</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0051</v>
+        <v>-0.0002</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.153</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1622</v>
+        <v>-0.1304</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.866</v>
+        <v>-3.912</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5386</v>
+        <v>-0.489</v>
       </c>
       <c r="J160" t="n">
-        <v>-16.158</v>
+        <v>-14.67</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.837</v>
+        <v>-0.8</v>
       </c>
       <c r="J161" t="n">
-        <v>-25.11</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.04</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2154</v>
+        <v>0.2033</v>
       </c>
       <c r="J162" t="n">
-        <v>4.9542</v>
+        <v>4.6759</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0098</v>
+        <v>-0.0402</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.2254</v>
+        <v>-0.9246</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.82</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.237</v>
+        <v>-0.1905</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.451</v>
+        <v>-4.3815</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2707</v>
+        <v>-0.2108</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.2261</v>
+        <v>-4.8484</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.18</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0965</v>
+        <v>-0.7845</v>
       </c>
       <c r="J166" t="n">
-        <v>-25.2195</v>
+        <v>-18.0435</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.67</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4784</v>
+        <v>1.3167</v>
       </c>
       <c r="J167" t="n">
-        <v>34.0032</v>
+        <v>30.2841</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.44</v>
       </c>
       <c r="I168" t="n">
-        <v>1.022</v>
+        <v>1.0354</v>
       </c>
       <c r="J168" t="n">
-        <v>23.506</v>
+        <v>23.8142</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7736</v>
+        <v>0.8524</v>
       </c>
       <c r="J169" t="n">
-        <v>17.7928</v>
+        <v>19.6052</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.16</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3348</v>
+        <v>0.4294</v>
       </c>
       <c r="J170" t="n">
-        <v>7.7004</v>
+        <v>9.876200000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.15</v>
       </c>
       <c r="I171" t="n">
-        <v>0.3094</v>
+        <v>0.4033</v>
       </c>
       <c r="J171" t="n">
-        <v>7.1162</v>
+        <v>9.2759</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0051</v>
+        <v>0.9885</v>
       </c>
       <c r="J172" t="n">
-        <v>26.1326</v>
+        <v>25.701</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.14</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4064</v>
+        <v>0.4222</v>
       </c>
       <c r="J173" t="n">
-        <v>10.5664</v>
+        <v>10.9772</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.11</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3033</v>
+        <v>0.3439</v>
       </c>
       <c r="J174" t="n">
-        <v>7.8858</v>
+        <v>8.9414</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.08</v>
       </c>
       <c r="I175" t="n">
-        <v>0.21</v>
+        <v>0.2594</v>
       </c>
       <c r="J175" t="n">
-        <v>5.46</v>
+        <v>6.7444</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1997</v>
+        <v>-0.1288</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.1922</v>
+        <v>-3.3488</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.11</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2742</v>
+        <v>0.2902</v>
       </c>
       <c r="J177" t="n">
-        <v>7.1292</v>
+        <v>7.5452</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1061</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.7586</v>
+        <v>-2.1216</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1279</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.3254</v>
+        <v>-2.4232</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2678</v>
+        <v>-0.1685</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.9628</v>
+        <v>-4.381</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.77</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4071</v>
+        <v>-0.2593</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.5846</v>
+        <v>-6.7418</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.75</v>
       </c>
       <c r="I182" t="n">
-        <v>1.6446</v>
+        <v>1.4229</v>
       </c>
       <c r="J182" t="n">
-        <v>37.8258</v>
+        <v>32.7267</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0884</v>
+        <v>1.069</v>
       </c>
       <c r="J183" t="n">
-        <v>25.0332</v>
+        <v>24.587</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.34</v>
       </c>
       <c r="I184" t="n">
-        <v>0.821</v>
+        <v>0.8586</v>
       </c>
       <c r="J184" t="n">
-        <v>18.883</v>
+        <v>19.7478</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1359</v>
+        <v>0.2197</v>
       </c>
       <c r="J185" t="n">
-        <v>3.1257</v>
+        <v>5.0531</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.9</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5042</v>
+        <v>-0.4285</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.5966</v>
+        <v>-9.855499999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.89</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1266</v>
+        <v>-0.1177</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.9118</v>
+        <v>-2.7071</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2985</v>
+        <v>-0.2227</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.8655</v>
+        <v>-5.1221</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2985</v>
+        <v>-0.2227</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.8655</v>
+        <v>-5.1221</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4289</v>
+        <v>-0.2879</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.864699999999999</v>
+        <v>-6.6217</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4892</v>
+        <v>-0.3257</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2516</v>
+        <v>-7.4911</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.68</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9142</v>
+        <v>0.8303</v>
       </c>
       <c r="J192" t="n">
-        <v>23.7692</v>
+        <v>21.5878</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.39</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5857</v>
+        <v>0.5107</v>
       </c>
       <c r="J193" t="n">
-        <v>15.2282</v>
+        <v>13.2782</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1685</v>
+        <v>0.1715</v>
       </c>
       <c r="J194" t="n">
-        <v>4.381</v>
+        <v>4.459</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3561</v>
+        <v>-0.2147</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.258599999999999</v>
+        <v>-5.5822</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4924</v>
+        <v>-0.3138</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.8024</v>
+        <v>-8.158799999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7521</v>
+        <v>0.7186</v>
       </c>
       <c r="J197" t="n">
-        <v>19.5546</v>
+        <v>18.6836</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.96</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0696</v>
+        <v>-0.058</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.8096</v>
+        <v>-1.508</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2724</v>
+        <v>-0.1698</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.0824</v>
+        <v>-4.4148</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.71</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4937</v>
+        <v>-0.3189</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.8362</v>
+        <v>-8.291399999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.67</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5467</v>
+        <v>-0.3569</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.2142</v>
+        <v>-9.279400000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.28</v>
       </c>
       <c r="I202" t="n">
-        <v>0.478</v>
+        <v>0.5657</v>
       </c>
       <c r="J202" t="n">
-        <v>20.076</v>
+        <v>23.7594</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4646</v>
+        <v>0.5483</v>
       </c>
       <c r="J203" t="n">
-        <v>19.5132</v>
+        <v>23.0286</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1524</v>
+        <v>-0.0808</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.4008</v>
+        <v>-3.3936</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.87</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2901</v>
+        <v>-0.1723</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.1842</v>
+        <v>-7.2366</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.87</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2901</v>
+        <v>-0.1723</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.1842</v>
+        <v>-7.2366</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0301</v>
+        <v>0.999</v>
       </c>
       <c r="J207" t="n">
-        <v>43.2642</v>
+        <v>41.958</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4166</v>
+        <v>0.3726</v>
       </c>
       <c r="J208" t="n">
-        <v>17.4972</v>
+        <v>15.6492</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.08</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3253</v>
+        <v>0.2857</v>
       </c>
       <c r="J209" t="n">
-        <v>13.6626</v>
+        <v>11.9994</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5967</v>
+        <v>-0.5464</v>
       </c>
       <c r="J210" t="n">
-        <v>-25.0614</v>
+        <v>-22.9488</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9024</v>
       </c>
       <c r="J211" t="n">
-        <v>-39.144</v>
+        <v>-37.9008</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.18</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3751</v>
+        <v>0.4214</v>
       </c>
       <c r="J212" t="n">
-        <v>11.253</v>
+        <v>12.642</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0699</v>
+        <v>0.0488</v>
       </c>
       <c r="J213" t="n">
-        <v>2.097</v>
+        <v>1.464</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0973</v>
+        <v>-0.0712</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.919</v>
+        <v>-2.136</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2916</v>
+        <v>-0.1812</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.747999999999999</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.482</v>
+        <v>-0.3103</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.46</v>
+        <v>-9.308999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.954</v>
+        <v>0.9287</v>
       </c>
       <c r="J217" t="n">
-        <v>28.62</v>
+        <v>27.861</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.597</v>
+        <v>0.5556</v>
       </c>
       <c r="J218" t="n">
-        <v>17.91</v>
+        <v>16.668</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I219" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="J219" t="n">
-        <v>2.202</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5782</v>
+        <v>-0.5249</v>
       </c>
       <c r="J220" t="n">
-        <v>-17.346</v>
+        <v>-15.747</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7044</v>
+        <v>-0.6566</v>
       </c>
       <c r="J221" t="n">
-        <v>-21.132</v>
+        <v>-19.698</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>0.274</v>
+        <v>0.2962</v>
       </c>
       <c r="J222" t="n">
-        <v>7.672</v>
+        <v>8.2936</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.08</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2062</v>
+        <v>0.2135</v>
       </c>
       <c r="J223" t="n">
-        <v>5.7736</v>
+        <v>5.978</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0131</v>
+        <v>-0.0182</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.3668</v>
+        <v>-0.5096000000000001</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.119</v>
+        <v>-0.0728</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.332</v>
+        <v>-2.0384</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5269</v>
+        <v>-0.3418</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.7532</v>
+        <v>-9.570399999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2205</v>
+        <v>1.1358</v>
       </c>
       <c r="J227" t="n">
-        <v>34.174</v>
+        <v>31.8024</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.24</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6925</v>
+        <v>0.6743</v>
       </c>
       <c r="J228" t="n">
-        <v>19.39</v>
+        <v>18.8804</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0858</v>
+        <v>0.1381</v>
       </c>
       <c r="J229" t="n">
-        <v>2.4024</v>
+        <v>3.8668</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2671</v>
+        <v>-0.1973</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.4788</v>
+        <v>-5.5244</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4514</v>
+        <v>-0.3838</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.6392</v>
+        <v>-10.7464</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.78</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2533</v>
+        <v>-0.2132</v>
       </c>
       <c r="J232" t="n">
-        <v>-5.5726</v>
+        <v>-4.6904</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.75</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3008</v>
+        <v>-0.2441</v>
       </c>
       <c r="J233" t="n">
-        <v>-6.6176</v>
+        <v>-5.3702</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.7</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3818</v>
+        <v>-0.2931</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.3996</v>
+        <v>-6.4482</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3989</v>
+        <v>-0.3025</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.7758</v>
+        <v>-6.655</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.41</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8183</v>
+        <v>-0.5617</v>
       </c>
       <c r="J236" t="n">
-        <v>-18.0026</v>
+        <v>-12.3574</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>1.9137</v>
+        <v>1.6178</v>
       </c>
       <c r="J237" t="n">
-        <v>42.1014</v>
+        <v>35.5916</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.66</v>
       </c>
       <c r="I238" t="n">
-        <v>1.3931</v>
+        <v>1.2784</v>
       </c>
       <c r="J238" t="n">
-        <v>30.6482</v>
+        <v>28.1248</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.4</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8267</v>
+        <v>0.9518</v>
       </c>
       <c r="J239" t="n">
-        <v>18.1874</v>
+        <v>20.9396</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.27</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5445</v>
+        <v>0.6663</v>
       </c>
       <c r="J240" t="n">
-        <v>11.979</v>
+        <v>14.6586</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.23</v>
       </c>
       <c r="I241" t="n">
-        <v>0.4544</v>
+        <v>0.5716</v>
       </c>
       <c r="J241" t="n">
-        <v>9.9968</v>
+        <v>12.5752</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4104</v>
+        <v>0.464</v>
       </c>
       <c r="J242" t="n">
-        <v>9.4392</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0936</v>
+        <v>0.0643</v>
       </c>
       <c r="J243" t="n">
-        <v>2.1528</v>
+        <v>1.4789</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1658</v>
+        <v>-0.1233</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.8134</v>
+        <v>-2.8359</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.7</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4958</v>
+        <v>-0.3224</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.4034</v>
+        <v>-7.4152</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.63</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5886</v>
+        <v>-0.3884</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.5378</v>
+        <v>-8.933199999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.47</v>
       </c>
       <c r="I247" t="n">
-        <v>1.12</v>
+        <v>1.0854</v>
       </c>
       <c r="J247" t="n">
-        <v>25.76</v>
+        <v>24.9642</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.39</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9496</v>
+        <v>0.967</v>
       </c>
       <c r="J248" t="n">
-        <v>21.8408</v>
+        <v>22.241</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.36</v>
       </c>
       <c r="I249" t="n">
-        <v>0.8821</v>
+        <v>0.9065</v>
       </c>
       <c r="J249" t="n">
-        <v>20.2883</v>
+        <v>20.8495</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.25</v>
       </c>
       <c r="I250" t="n">
-        <v>0.5914</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J250" t="n">
-        <v>13.6022</v>
+        <v>15.2674</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.95</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3536</v>
+        <v>-0.2708</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.1328</v>
+        <v>-6.2284</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>2.08</v>
       </c>
       <c r="I252" t="n">
-        <v>2.0067</v>
+        <v>1.7213</v>
       </c>
       <c r="J252" t="n">
-        <v>38.1273</v>
+        <v>32.7047</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.79</v>
       </c>
       <c r="I253" t="n">
-        <v>1.5758</v>
+        <v>1.4066</v>
       </c>
       <c r="J253" t="n">
-        <v>29.9402</v>
+        <v>26.7254</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.55</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0802</v>
+        <v>1.1404</v>
       </c>
       <c r="J254" t="n">
-        <v>20.5238</v>
+        <v>21.6676</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.43</v>
       </c>
       <c r="I255" t="n">
-        <v>0.84</v>
+        <v>0.9845</v>
       </c>
       <c r="J255" t="n">
-        <v>15.96</v>
+        <v>18.7055</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.36</v>
       </c>
       <c r="I256" t="n">
-        <v>0.6976</v>
+        <v>0.8429</v>
       </c>
       <c r="J256" t="n">
-        <v>13.2544</v>
+        <v>16.0151</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.68</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.3</v>
+        <v>-0.2578</v>
       </c>
       <c r="J257" t="n">
-        <v>-5.7</v>
+        <v>-4.8982</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.54</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.5173</v>
+        <v>-0.4063</v>
       </c>
       <c r="J258" t="n">
-        <v>-9.8287</v>
+        <v>-7.7197</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.52</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.551</v>
+        <v>-0.4256</v>
       </c>
       <c r="J259" t="n">
-        <v>-10.469</v>
+        <v>-8.086399999999999</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.41</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.7567</v>
+        <v>-0.5262</v>
       </c>
       <c r="J260" t="n">
-        <v>-14.3773</v>
+        <v>-9.9978</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.28</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.9403</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="J261" t="n">
-        <v>-17.8657</v>
+        <v>-12.4583</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4083/event_4083_evp_summary.xlsx
+++ b/database/event/4083/event_4083_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4333</v>
+        <v>5.6268</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0049</v>
+        <v>2.0763</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8148</v>
+        <v>1.9372</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4333</v>
+        <v>5.6268</v>
       </c>
       <c r="F2" t="n">
-        <v>3.094</v>
+        <v>3.0836</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3393</v>
+        <v>2.5432</v>
       </c>
       <c r="H2" t="n">
-        <v>5.415</v>
+        <v>5.2797</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8156</v>
+        <v>2.851</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3393</v>
+        <v>2.5432</v>
       </c>
       <c r="K2" t="n">
         <v>176</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1549</v>
+        <v>5.3942</v>
       </c>
       <c r="N2" t="n">
         <v>319</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.178</v>
+        <v>5.2419</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9107</v>
+        <v>1.9343</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6996</v>
+        <v>1.762</v>
       </c>
       <c r="E3" t="n">
-        <v>5.178</v>
+        <v>5.2419</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4525</v>
+        <v>2.3641</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7255</v>
+        <v>2.8778</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1547</v>
+        <v>2.9058</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6403</v>
+        <v>1.5691</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7255</v>
+        <v>2.8778</v>
       </c>
       <c r="K3" t="n">
         <v>176</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3658</v>
+        <v>4.4469</v>
       </c>
       <c r="N3" t="n">
         <v>319</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8095</v>
+        <v>4.8811</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7747</v>
+        <v>1.8012</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5332</v>
+        <v>1.5978</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8095</v>
+        <v>4.8811</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3084</v>
+        <v>2.2253</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5011</v>
+        <v>2.6558</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6472</v>
+        <v>2.448</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3764</v>
+        <v>1.3219</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5011</v>
+        <v>2.6558</v>
       </c>
       <c r="K4" t="n">
         <v>121</v>
@@ -621,7 +621,7 @@
         <v>139</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8775</v>
+        <v>3.9777</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3943</v>
+        <v>4.3108</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6215</v>
+        <v>1.5907</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3458</v>
+        <v>1.3382</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3943</v>
+        <v>4.3108</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4299</v>
+        <v>2.3081</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9644</v>
+        <v>2.0027</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0751</v>
+        <v>2.721</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5989</v>
+        <v>1.4693</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9644</v>
+        <v>2.0027</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5633</v>
+        <v>3.472</v>
       </c>
       <c r="N5" t="n">
         <v>260</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1274</v>
+        <v>4.1281</v>
       </c>
       <c r="C6" t="n">
-        <v>1.523</v>
+        <v>1.5233</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2253</v>
+        <v>1.255</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1274</v>
+        <v>4.1281</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6504</v>
+        <v>2.574</v>
       </c>
       <c r="G6" t="n">
-        <v>1.477</v>
+        <v>1.5541</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8519</v>
+        <v>3.5984</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0028</v>
+        <v>1.9431</v>
       </c>
       <c r="J6" t="n">
-        <v>1.477</v>
+        <v>1.5541</v>
       </c>
       <c r="K6" t="n">
         <v>176</v>
@@ -713,7 +713,7 @@
         <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4798</v>
+        <v>3.4972</v>
       </c>
       <c r="N6" t="n">
         <v>319</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.033</v>
+        <v>4.0391</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4882</v>
+        <v>1.4905</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1827</v>
+        <v>1.2145</v>
       </c>
       <c r="E7" t="n">
-        <v>4.033</v>
+        <v>4.0391</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7257</v>
+        <v>2.6458</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3073</v>
+        <v>1.3933</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1173</v>
+        <v>3.8354</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1408</v>
+        <v>2.0711</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3073</v>
+        <v>1.3933</v>
       </c>
       <c r="K7" t="n">
         <v>176</v>
@@ -759,7 +759,7 @@
         <v>143</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4481</v>
+        <v>3.4644</v>
       </c>
       <c r="N7" t="n">
         <v>319</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6679</v>
+        <v>3.5745</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3535</v>
+        <v>1.319</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0179</v>
+        <v>1.003</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6679</v>
+        <v>3.5745</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8992</v>
+        <v>2.8229</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7687</v>
+        <v>0.7516</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7287</v>
+        <v>4.4197</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4587</v>
+        <v>2.3866</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7687</v>
+        <v>0.7516</v>
       </c>
       <c r="K8" t="n">
         <v>175</v>
@@ -805,7 +805,7 @@
         <v>67</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2274</v>
+        <v>3.1382</v>
       </c>
       <c r="N8" t="n">
         <v>242</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3362</v>
+        <v>3.4841</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2311</v>
+        <v>1.2857</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8681</v>
+        <v>0.9618</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3362</v>
+        <v>3.4841</v>
       </c>
       <c r="F9" t="n">
-        <v>2.251</v>
+        <v>2.1972</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0852</v>
+        <v>1.2869</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4448</v>
+        <v>2.3552</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2712</v>
+        <v>1.2718</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0852</v>
+        <v>1.2869</v>
       </c>
       <c r="K9" t="n">
         <v>176</v>
@@ -851,7 +851,7 @@
         <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3564</v>
+        <v>2.5587</v>
       </c>
       <c r="N9" t="n">
         <v>319</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2877</v>
+        <v>3.2551</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2132</v>
+        <v>1.2012</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8462</v>
+        <v>0.8576</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2877</v>
+        <v>3.2551</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3851</v>
+        <v>3.3775</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0974</v>
+        <v>-0.1224</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4406</v>
+        <v>6.2495</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3488</v>
+        <v>3.3747</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0974</v>
+        <v>-0.1224</v>
       </c>
       <c r="K10" t="n">
         <v>71</v>
@@ -897,7 +897,7 @@
         <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2514</v>
+        <v>3.2523</v>
       </c>
       <c r="N10" t="n">
         <v>142</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6974</v>
+        <v>2.4383</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9954</v>
+        <v>0.8998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5797</v>
+        <v>0.4858</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6974</v>
+        <v>2.4383</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6974</v>
+        <v>2.4383</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6974</v>
+        <v>2.6117</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6974</v>
+        <v>2.6117</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6974</v>
+        <v>2.6117</v>
       </c>
       <c r="N11" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.687</v>
+        <v>2.427</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9915</v>
+        <v>0.8956</v>
       </c>
       <c r="D12" t="n">
-        <v>0.575</v>
+        <v>0.4806</v>
       </c>
       <c r="E12" t="n">
-        <v>2.687</v>
+        <v>2.427</v>
       </c>
       <c r="F12" t="n">
-        <v>2.687</v>
+        <v>2.427</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.687</v>
+        <v>2.5871</v>
       </c>
       <c r="I12" t="n">
-        <v>2.687</v>
+        <v>2.5871</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.687</v>
+        <v>2.5871</v>
       </c>
       <c r="N12" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3923</v>
+        <v>2.3024</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8828</v>
+        <v>0.8496</v>
       </c>
       <c r="D13" t="n">
-        <v>0.442</v>
+        <v>0.4239</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3923</v>
+        <v>2.3024</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9364</v>
+        <v>2.8413</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5441</v>
+        <v>-0.5389</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8599</v>
+        <v>4.4803</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5269</v>
+        <v>2.4193</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5441</v>
+        <v>-0.5389</v>
       </c>
       <c r="K13" t="n">
         <v>121</v>
@@ -1035,7 +1035,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9828</v>
+        <v>1.8804</v>
       </c>
       <c r="N13" t="n">
         <v>260</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3061</v>
+        <v>2.2448</v>
       </c>
       <c r="C14" t="n">
-        <v>0.851</v>
+        <v>0.8284</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4031</v>
+        <v>0.3977</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3061</v>
+        <v>2.2448</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6053</v>
+        <v>2.5602</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2992</v>
+        <v>-0.3154</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6932</v>
+        <v>3.553</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9203</v>
+        <v>1.9186</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2992</v>
+        <v>-0.3154</v>
       </c>
       <c r="K14" t="n">
         <v>71</v>
@@ -1081,7 +1081,7 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6211</v>
+        <v>1.6032</v>
       </c>
       <c r="N14" t="n">
         <v>142</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1109</v>
+        <v>2.0419</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7789</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.315</v>
+        <v>0.3053</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1109</v>
+        <v>2.0419</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4356</v>
+        <v>2.3608</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3247</v>
+        <v>-0.3189</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0951</v>
+        <v>2.8949</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6093</v>
+        <v>1.5632</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3247</v>
+        <v>-0.3189</v>
       </c>
       <c r="K15" t="n">
         <v>175</v>
@@ -1127,7 +1127,7 @@
         <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2846</v>
+        <v>1.2443</v>
       </c>
       <c r="N15" t="n">
         <v>242</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0749</v>
+        <v>1.9559</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7657</v>
+        <v>0.7217</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2987</v>
+        <v>0.2662</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0749</v>
+        <v>1.9559</v>
       </c>
       <c r="F16" t="n">
-        <v>2.475</v>
+        <v>2.3795</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4001</v>
+        <v>-0.4236</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2341</v>
+        <v>2.9567</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6816</v>
+        <v>1.5966</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4001</v>
+        <v>-0.4236</v>
       </c>
       <c r="K16" t="n">
         <v>71</v>
@@ -1173,7 +1173,7 @@
         <v>71</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2815</v>
+        <v>1.173</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0439</v>
+        <v>1.9466</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7542</v>
+        <v>0.7183</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2847</v>
+        <v>0.2619</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0439</v>
+        <v>1.9466</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0439</v>
+        <v>2.9466</v>
       </c>
       <c r="G17" t="n">
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2385</v>
+        <v>4.8279</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7238</v>
+        <v>2.607</v>
       </c>
       <c r="J17" t="n">
         <v>-1</v>
@@ -1219,7 +1219,7 @@
         <v>71</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7238</v>
+        <v>1.607</v>
       </c>
       <c r="N17" t="n">
         <v>142</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5986</v>
+        <v>1.4983</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5899</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0837</v>
+        <v>0.0579</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5986</v>
+        <v>1.4983</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5986</v>
+        <v>1.4983</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5986</v>
+        <v>1.4983</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5986</v>
+        <v>1.4983</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5986</v>
+        <v>1.4983</v>
       </c>
       <c r="N18" t="n">
         <v>173</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3124</v>
+        <v>1.3156</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4843</v>
+        <v>0.4855</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0455</v>
+        <v>-0.0253</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3124</v>
+        <v>1.3156</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7941</v>
+        <v>0.7163</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5183</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7941</v>
+        <v>0.7163</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4129</v>
+        <v>0.3868</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5183</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>175</v>
@@ -1311,7 +1311,7 @@
         <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9312</v>
+        <v>0.9861</v>
       </c>
       <c r="N19" t="n">
         <v>242</v>
@@ -1320,369 +1320,369 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8515</v>
+        <v>1.0073</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3142</v>
+        <v>0.3717</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2536</v>
+        <v>-0.1657</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8515</v>
+        <v>1.0073</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8515</v>
+        <v>-1.3845</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.3918</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8515</v>
+        <v>-1.3845</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8515</v>
+        <v>-0.7476</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.3918</v>
       </c>
       <c r="K20" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8515</v>
+        <v>1.6442</v>
       </c>
       <c r="N20" t="n">
-        <v>135</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7356</v>
+        <v>0.7922</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2714</v>
+        <v>0.2923</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3059</v>
+        <v>-0.2636</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7356</v>
+        <v>0.7922</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4701</v>
+        <v>0.7922</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2058</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4701</v>
+        <v>0.7922</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7644</v>
+        <v>0.7922</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2058</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L21" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4414</v>
+        <v>0.7922</v>
       </c>
       <c r="N21" t="n">
-        <v>260</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6253</v>
+        <v>0.5858</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2307</v>
+        <v>0.2162</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3557</v>
+        <v>-0.3575</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6253</v>
+        <v>0.5858</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6253</v>
+        <v>0.8093</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.2235</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6253</v>
+        <v>0.8093</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6253</v>
+        <v>0.437</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.2235</v>
       </c>
       <c r="K22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6253</v>
+        <v>0.2135</v>
       </c>
       <c r="N22" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5802</v>
+        <v>0.5563</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2141</v>
+        <v>0.2053</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3761</v>
+        <v>-0.371</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5802</v>
+        <v>0.5563</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7741</v>
+        <v>0.5563</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7741</v>
+        <v>0.5563</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4025</v>
+        <v>0.5563</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2086</v>
+        <v>0.5563</v>
       </c>
       <c r="N23" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4618</v>
+        <v>0.4564</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1704</v>
+        <v>0.1684</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4295</v>
+        <v>-0.4164</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4618</v>
+        <v>0.4564</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4618</v>
+        <v>0.4564</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4618</v>
+        <v>0.4564</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4618</v>
+        <v>0.4564</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4618</v>
+        <v>0.4564</v>
       </c>
       <c r="N24" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4331</v>
+        <v>0.3807</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1598</v>
+        <v>0.1405</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4425</v>
+        <v>-0.4509</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4331</v>
+        <v>0.3807</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4331</v>
+        <v>0.3807</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4331</v>
+        <v>0.3807</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4331</v>
+        <v>0.3807</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4331</v>
+        <v>0.3807</v>
       </c>
       <c r="N25" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.342</v>
+        <v>0.2608</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1262</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4836</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.342</v>
+        <v>0.2608</v>
       </c>
       <c r="F26" t="n">
-        <v>0.342</v>
+        <v>0.2608</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.342</v>
+        <v>0.2608</v>
       </c>
       <c r="I26" t="n">
-        <v>0.342</v>
+        <v>0.2608</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.342</v>
+        <v>0.2608</v>
       </c>
       <c r="N26" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2953</v>
+        <v>0.2578</v>
       </c>
       <c r="C27" t="n">
-        <v>0.109</v>
+        <v>0.0951</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5047</v>
+        <v>-0.5068</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2953</v>
+        <v>0.2578</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2953</v>
+        <v>0.2578</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2953</v>
+        <v>0.2578</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2953</v>
+        <v>0.2578</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2953</v>
+        <v>0.2578</v>
       </c>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2468</v>
+        <v>0.2324</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0911</v>
+        <v>0.0858</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5266</v>
+        <v>-0.5184</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2468</v>
+        <v>0.2324</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2468</v>
+        <v>0.2324</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2468</v>
+        <v>0.2324</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2468</v>
+        <v>0.2324</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2468</v>
+        <v>0.2324</v>
       </c>
       <c r="N28" t="n">
         <v>81</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0717</v>
+        <v>0.0219</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0265</v>
+        <v>0.0081</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6056</v>
+        <v>-0.6142</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0717</v>
+        <v>0.0219</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0717</v>
+        <v>0.0219</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0717</v>
+        <v>0.0219</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0717</v>
+        <v>0.0219</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0717</v>
+        <v>0.0219</v>
       </c>
       <c r="N29" t="n">
         <v>173</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.047</v>
+        <v>-0.0145</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0173</v>
+        <v>-0.0054</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6168</v>
+        <v>-0.6308</v>
       </c>
       <c r="E30" t="n">
-        <v>0.047</v>
+        <v>-0.0145</v>
       </c>
       <c r="F30" t="n">
-        <v>0.047</v>
+        <v>-0.0145</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.047</v>
+        <v>-0.0145</v>
       </c>
       <c r="I30" t="n">
-        <v>0.047</v>
+        <v>-0.0145</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.047</v>
+        <v>-0.0145</v>
       </c>
       <c r="N30" t="n">
         <v>72</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1618</v>
+        <v>-0.1904</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0597</v>
+        <v>-0.0703</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7111</v>
+        <v>-0.7109</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1618</v>
+        <v>-0.1904</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1618</v>
+        <v>-0.1904</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1618</v>
+        <v>-0.1904</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1618</v>
+        <v>-0.1904</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1618</v>
+        <v>-0.1904</v>
       </c>
       <c r="N31" t="n">
         <v>81</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4154</v>
+        <v>-0.4844</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1533</v>
+        <v>-0.1787</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8255</v>
+        <v>-0.8447</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4154</v>
+        <v>-0.4844</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3183</v>
+        <v>0.2478</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7337</v>
+        <v>-0.7322</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3183</v>
+        <v>0.2478</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1655</v>
+        <v>0.1338</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7337</v>
+        <v>-0.7322</v>
       </c>
       <c r="K32" t="n">
         <v>175</v>
@@ -1909,7 +1909,7 @@
         <v>67</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5682</v>
+        <v>-0.5983999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>242</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5743</v>
+        <v>-0.5878</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2119</v>
+        <v>-0.2169</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8973</v>
+        <v>-0.8918</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5743</v>
+        <v>-0.5878</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5743</v>
+        <v>-0.5878</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5743</v>
+        <v>-0.5878</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5743</v>
+        <v>-0.5878</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5743</v>
+        <v>-0.5878</v>
       </c>
       <c r="N33" t="n">
         <v>135</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6007</v>
+        <v>-0.6312</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2217</v>
+        <v>-0.2329</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9092</v>
+        <v>-0.9115</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6007</v>
+        <v>-0.6312</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6007</v>
+        <v>-0.6312</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6007</v>
+        <v>-0.6312</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6007</v>
+        <v>-0.6312</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6007</v>
+        <v>-0.6312</v>
       </c>
       <c r="N34" t="n">
         <v>81</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6925</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2442</v>
+        <v>-0.2555</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9368</v>
+        <v>-0.9394</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6925</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6925</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6925</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6925</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6925</v>
       </c>
       <c r="N35" t="n">
         <v>81</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7417</v>
+        <v>-0.7751</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2737</v>
+        <v>-0.286</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9729</v>
+        <v>-0.977</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7417</v>
+        <v>-0.7751</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7417</v>
+        <v>-0.7751</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7417</v>
+        <v>-0.7751</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7417</v>
+        <v>-0.7751</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7417</v>
+        <v>-0.7751</v>
       </c>
       <c r="N36" t="n">
         <v>72</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7421</v>
+        <v>-0.7936</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2738</v>
+        <v>-0.2928</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.973</v>
+        <v>-0.9855</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7421</v>
+        <v>-0.7936</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7421</v>
+        <v>-0.7936</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7421</v>
+        <v>-0.7936</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7421</v>
+        <v>-0.7936</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7421</v>
+        <v>-0.7936</v>
       </c>
       <c r="N37" t="n">
         <v>72</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0282</v>
+        <v>-1.0122</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3794</v>
+        <v>-0.3735</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1022</v>
+        <v>-1.085</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0282</v>
+        <v>-1.0122</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9749</v>
+        <v>-1.0122</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9749</v>
+        <v>-1.0122</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5069</v>
+        <v>-1.0122</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L38" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.5602</v>
+        <v>-1.0122</v>
       </c>
       <c r="N38" t="n">
-        <v>242</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0751</v>
+        <v>-1.0832</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3967</v>
+        <v>-0.3997</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1234</v>
+        <v>-1.1173</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0751</v>
+        <v>-1.0832</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0751</v>
+        <v>-1.0409</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.0423</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0751</v>
+        <v>-1.0409</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0751</v>
+        <v>-0.5621</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.0423</v>
       </c>
       <c r="K39" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0751</v>
+        <v>-0.6044</v>
       </c>
       <c r="N39" t="n">
-        <v>173</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.614</v>
+        <v>-1.6162</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5956</v>
+        <v>-0.5964</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3667</v>
+        <v>-1.3599</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.614</v>
+        <v>-1.6162</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.614</v>
+        <v>-1.6162</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.614</v>
+        <v>-1.6162</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.614</v>
+        <v>-1.6162</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.614</v>
+        <v>-1.6162</v>
       </c>
       <c r="N40" t="n">
         <v>72</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2107</v>
+        <v>-1.9038</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8158</v>
+        <v>-0.7025</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.636</v>
+        <v>-1.4909</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2107</v>
+        <v>-1.9038</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8682</v>
+        <v>-1.7156</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3425</v>
+        <v>-0.1882</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8682</v>
+        <v>-1.7156</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9714</v>
+        <v>-0.9264</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3425</v>
+        <v>-0.1882</v>
       </c>
       <c r="K41" t="n">
         <v>121</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3139</v>
+        <v>-1.1146</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3661</v>
+        <v>0.3603</v>
       </c>
       <c r="J2" t="n">
-        <v>10.983</v>
+        <v>10.809</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3378</v>
+        <v>0.3343</v>
       </c>
       <c r="J3" t="n">
-        <v>10.134</v>
+        <v>10.029</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0956</v>
       </c>
       <c r="J4" t="n">
-        <v>2.637</v>
+        <v>2.868</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0044</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.195</v>
+        <v>-0.132</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2383</v>
+        <v>-0.2368</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.149</v>
+        <v>-7.104</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9849</v>
+        <v>0.9401</v>
       </c>
       <c r="J7" t="n">
-        <v>29.547</v>
+        <v>28.203</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.104</v>
+        <v>0.116</v>
       </c>
       <c r="J8" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0285</v>
+        <v>-0.0313</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.855</v>
+        <v>-0.9389999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0793</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.16</v>
+        <v>-2.379</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1547</v>
+        <v>-0.1656</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.641</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6762</v>
+        <v>0.6448</v>
       </c>
       <c r="J12" t="n">
-        <v>28.4004</v>
+        <v>27.0816</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6272</v>
+        <v>0.6014</v>
       </c>
       <c r="J13" t="n">
-        <v>26.3424</v>
+        <v>25.2588</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4254</v>
+        <v>0.4196</v>
       </c>
       <c r="J14" t="n">
-        <v>17.8668</v>
+        <v>17.6232</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2639</v>
+        <v>0.2698</v>
       </c>
       <c r="J15" t="n">
-        <v>11.0838</v>
+        <v>11.3316</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3529</v>
+        <v>-0.3382</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.8218</v>
+        <v>-14.2044</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5936</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>24.9312</v>
+        <v>24.3642</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2124</v>
+        <v>0.223</v>
       </c>
       <c r="J18" t="n">
-        <v>8.9208</v>
+        <v>9.366</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1923</v>
+        <v>0.2034</v>
       </c>
       <c r="J19" t="n">
-        <v>8.076599999999999</v>
+        <v>8.5428</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0267</v>
+        <v>-0.0299</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1214</v>
+        <v>-1.2558</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1637</v>
+        <v>-0.1752</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.8754</v>
+        <v>-7.3584</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.25</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6514</v>
+        <v>1.7952</v>
       </c>
       <c r="J22" t="n">
-        <v>29.7252</v>
+        <v>32.3136</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.67</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0108</v>
+        <v>1.1224</v>
       </c>
       <c r="J23" t="n">
-        <v>18.1944</v>
+        <v>20.2032</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.52</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8404</v>
+        <v>0.9383</v>
       </c>
       <c r="J24" t="n">
-        <v>15.1272</v>
+        <v>16.8894</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.23</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4693</v>
+        <v>0.5301</v>
       </c>
       <c r="J25" t="n">
-        <v>8.4474</v>
+        <v>9.5418</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0771</v>
+        <v>0.1168</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3878</v>
+        <v>2.1024</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2702</v>
+        <v>0.2313</v>
       </c>
       <c r="J27" t="n">
-        <v>4.8636</v>
+        <v>4.1634</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.66</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3242</v>
+        <v>-0.3455</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.8356</v>
+        <v>-6.219</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.6</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3774</v>
+        <v>-0.3967</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.7932</v>
+        <v>-7.1406</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.49</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4797</v>
+        <v>-0.493</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.634600000000001</v>
+        <v>-8.874000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.36</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.603</v>
+        <v>-0.6073</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.854</v>
+        <v>-10.9314</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.331</v>
+        <v>0.3303</v>
       </c>
       <c r="J32" t="n">
-        <v>7.944</v>
+        <v>7.9272</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1561</v>
+        <v>0.1574</v>
       </c>
       <c r="J33" t="n">
-        <v>3.7464</v>
+        <v>3.7776</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2021</v>
+        <v>-0.2194</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.8504</v>
+        <v>-5.2656</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3062</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.9624</v>
+        <v>-7.3488</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.52</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4867</v>
+        <v>-0.4943</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.6808</v>
+        <v>-11.8632</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.7508</v>
       </c>
       <c r="J37" t="n">
-        <v>15.6648</v>
+        <v>18.0192</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3662</v>
+        <v>0.4051</v>
       </c>
       <c r="J38" t="n">
-        <v>8.7888</v>
+        <v>9.7224</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.2</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2721</v>
+        <v>0.292</v>
       </c>
       <c r="J39" t="n">
-        <v>6.5304</v>
+        <v>7.008</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2344</v>
+        <v>0.255</v>
       </c>
       <c r="J40" t="n">
-        <v>5.6256</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.08</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1109</v>
+        <v>0.1316</v>
       </c>
       <c r="J41" t="n">
-        <v>2.6616</v>
+        <v>3.1584</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.548</v>
+        <v>0.6019</v>
       </c>
       <c r="J42" t="n">
-        <v>13.7</v>
+        <v>15.0475</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4887</v>
+        <v>0.536</v>
       </c>
       <c r="J43" t="n">
-        <v>12.2175</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.13</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3808</v>
+        <v>0.405</v>
       </c>
       <c r="J44" t="n">
-        <v>9.52</v>
+        <v>10.125</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0127</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.3175</v>
+        <v>-0.2175</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8165</v>
+        <v>-0.7563</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.4125</v>
+        <v>-18.9075</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2641</v>
+        <v>0.2653</v>
       </c>
       <c r="J47" t="n">
-        <v>6.6025</v>
+        <v>6.6325</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.243</v>
+        <v>0.2452</v>
       </c>
       <c r="J48" t="n">
-        <v>6.075</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1543</v>
+        <v>0.1587</v>
       </c>
       <c r="J49" t="n">
-        <v>3.8575</v>
+        <v>3.9675</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.79</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2416</v>
+        <v>-0.2565</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.04</v>
+        <v>-6.4125</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.66</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3667</v>
+        <v>-0.3785</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.1675</v>
+        <v>-9.4625</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.93</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0735</v>
+        <v>-0.0911</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.6905</v>
+        <v>-2.0953</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0857</v>
+        <v>-0.1037</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.9711</v>
+        <v>-2.3851</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1953</v>
+        <v>-0.2142</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.4919</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.328</v>
+        <v>-0.3448</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.544</v>
+        <v>-7.9304</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.6</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4033</v>
+        <v>-0.4168</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.2759</v>
+        <v>-9.586399999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.57</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9296</v>
+        <v>1.0282</v>
       </c>
       <c r="J57" t="n">
-        <v>21.3808</v>
+        <v>23.6486</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.43</v>
       </c>
       <c r="I58" t="n">
-        <v>0.756</v>
+        <v>0.8409</v>
       </c>
       <c r="J58" t="n">
-        <v>17.388</v>
+        <v>19.3407</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.37</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6801</v>
+        <v>0.758</v>
       </c>
       <c r="J59" t="n">
-        <v>15.6423</v>
+        <v>17.434</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3641</v>
+        <v>0.3918</v>
       </c>
       <c r="J60" t="n">
-        <v>8.3743</v>
+        <v>9.0114</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1873</v>
+        <v>0.2094</v>
       </c>
       <c r="J61" t="n">
-        <v>4.3079</v>
+        <v>4.8162</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3378</v>
+        <v>0.3563</v>
       </c>
       <c r="J62" t="n">
-        <v>9.1206</v>
+        <v>9.620100000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2809</v>
+        <v>0.2956</v>
       </c>
       <c r="J63" t="n">
-        <v>7.5843</v>
+        <v>7.9812</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2162</v>
+        <v>0.2318</v>
       </c>
       <c r="J64" t="n">
-        <v>5.8374</v>
+        <v>6.2586</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1048</v>
+        <v>0.1188</v>
       </c>
       <c r="J65" t="n">
-        <v>2.8296</v>
+        <v>3.2076</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1883</v>
+        <v>-0.1994</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.0841</v>
+        <v>-5.3838</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4527</v>
+        <v>0.5023</v>
       </c>
       <c r="J67" t="n">
-        <v>12.2229</v>
+        <v>13.5621</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="J68" t="n">
-        <v>0.891</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0968</v>
+        <v>-0.109</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.6136</v>
+        <v>-2.943</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.5289</v>
+        <v>-3.8934</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3703</v>
+        <v>-0.3812</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.998100000000001</v>
+        <v>-10.2924</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.77</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.213</v>
+        <v>-0.2386</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.473</v>
+        <v>-5.0106</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.77</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.213</v>
+        <v>-0.2386</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.473</v>
+        <v>-5.0106</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3048</v>
+        <v>-0.3269</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.4008</v>
+        <v>-6.8649</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.53</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4417</v>
+        <v>-0.4575</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.275700000000001</v>
+        <v>-9.6075</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.38</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5836</v>
+        <v>-0.5895</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.2556</v>
+        <v>-12.3795</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.91</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2883</v>
+        <v>1.4152</v>
       </c>
       <c r="J77" t="n">
-        <v>27.0543</v>
+        <v>29.7192</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.63</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9701</v>
+        <v>1.0777</v>
       </c>
       <c r="J78" t="n">
-        <v>20.3721</v>
+        <v>22.6317</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.55</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.9779</v>
       </c>
       <c r="J79" t="n">
-        <v>18.4275</v>
+        <v>20.5359</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6233</v>
+        <v>0.6998</v>
       </c>
       <c r="J80" t="n">
-        <v>13.0893</v>
+        <v>14.6958</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.09</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2065</v>
+        <v>0.2366</v>
       </c>
       <c r="J81" t="n">
-        <v>4.3365</v>
+        <v>4.9686</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4558</v>
+        <v>1.4317</v>
       </c>
       <c r="J82" t="n">
-        <v>43.674</v>
+        <v>42.951</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.04</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1453</v>
+        <v>0.1559</v>
       </c>
       <c r="J83" t="n">
-        <v>4.359</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0741</v>
+        <v>0.0862</v>
       </c>
       <c r="J84" t="n">
-        <v>2.223</v>
+        <v>2.586</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.89</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4044</v>
+        <v>-0.3869</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.132</v>
+        <v>-11.607</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6481</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.443</v>
+        <v>-18.192</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.47</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8733</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>26.199</v>
+        <v>24.966</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.17</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3645</v>
+        <v>0.3684</v>
       </c>
       <c r="J88" t="n">
-        <v>10.935</v>
+        <v>11.052</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0059</v>
+        <v>-0.0045</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.177</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.88</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1639</v>
+        <v>-0.1754</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.917</v>
+        <v>-5.262</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.83</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2165</v>
+        <v>-0.2284</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.495</v>
+        <v>-6.852</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2861</v>
+        <v>0.2939</v>
       </c>
       <c r="J92" t="n">
-        <v>11.7301</v>
+        <v>12.0499</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1674</v>
+        <v>0.1783</v>
       </c>
       <c r="J93" t="n">
-        <v>6.8634</v>
+        <v>7.3103</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.026</v>
+        <v>0.0319</v>
       </c>
       <c r="J94" t="n">
-        <v>1.066</v>
+        <v>1.3079</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.01</v>
       </c>
       <c r="I95" t="n">
-        <v>0.026</v>
+        <v>0.0319</v>
       </c>
       <c r="J95" t="n">
-        <v>1.066</v>
+        <v>1.3079</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1597</v>
+        <v>-0.1721</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.5477</v>
+        <v>-7.0561</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.27</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3798</v>
+        <v>0.3913</v>
       </c>
       <c r="J97" t="n">
-        <v>15.5718</v>
+        <v>16.0433</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2291</v>
+        <v>0.2447</v>
       </c>
       <c r="J98" t="n">
-        <v>9.3931</v>
+        <v>10.0327</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2027</v>
+        <v>0.2185</v>
       </c>
       <c r="J99" t="n">
-        <v>8.310700000000001</v>
+        <v>8.958500000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.02</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0365</v>
+        <v>0.0467</v>
       </c>
       <c r="J100" t="n">
-        <v>1.4965</v>
+        <v>1.9147</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.93</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1107</v>
+        <v>-0.1198</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.5387</v>
+        <v>-4.9118</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7817</v>
+        <v>0.7448</v>
       </c>
       <c r="J102" t="n">
-        <v>21.1059</v>
+        <v>20.1096</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.29</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7591</v>
+        <v>0.7249</v>
       </c>
       <c r="J103" t="n">
-        <v>20.4957</v>
+        <v>19.5723</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.28</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7365</v>
+        <v>0.7049</v>
       </c>
       <c r="J104" t="n">
-        <v>19.8855</v>
+        <v>19.0323</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6446</v>
       </c>
       <c r="J105" t="n">
-        <v>18.0603</v>
+        <v>17.4042</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3468</v>
+        <v>0.3535</v>
       </c>
       <c r="J106" t="n">
-        <v>9.3636</v>
+        <v>9.544499999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2447</v>
+        <v>0.2414</v>
       </c>
       <c r="J107" t="n">
-        <v>6.6069</v>
+        <v>6.5178</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0363</v>
+        <v>-0.0477</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.9801</v>
+        <v>-1.2879</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1532</v>
+        <v>-0.1697</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.1364</v>
+        <v>-4.5819</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1532</v>
+        <v>-0.1697</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.1364</v>
+        <v>-4.5819</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4422</v>
+        <v>-0.452</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.9394</v>
+        <v>-12.204</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0525</v>
+        <v>0.9967</v>
       </c>
       <c r="J112" t="n">
-        <v>31.575</v>
+        <v>29.901</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.17</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5105</v>
+        <v>0.4951</v>
       </c>
       <c r="J113" t="n">
-        <v>15.315</v>
+        <v>14.853</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4847</v>
+        <v>0.4718</v>
       </c>
       <c r="J114" t="n">
-        <v>14.541</v>
+        <v>14.154</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2844</v>
+        <v>-0.2764</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.532</v>
+        <v>-8.292</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.77</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7236</v>
+        <v>-0.6734</v>
       </c>
       <c r="J116" t="n">
-        <v>-21.708</v>
+        <v>-20.202</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.22</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4865</v>
+        <v>0.4758</v>
       </c>
       <c r="J117" t="n">
-        <v>14.595</v>
+        <v>14.274</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.13</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3155</v>
+        <v>0.3164</v>
       </c>
       <c r="J118" t="n">
-        <v>9.465</v>
+        <v>9.492000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.96</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0605</v>
+        <v>-0.0704</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.815</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2551</v>
+        <v>-0.2691</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.653</v>
+        <v>-8.073</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2845</v>
+        <v>-0.298</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.535</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.31</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8567</v>
+        <v>0.8011</v>
       </c>
       <c r="J122" t="n">
-        <v>24.8443</v>
+        <v>23.2319</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6625</v>
+        <v>0.6306</v>
       </c>
       <c r="J123" t="n">
-        <v>19.2125</v>
+        <v>18.2874</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3524</v>
+        <v>0.351</v>
       </c>
       <c r="J124" t="n">
-        <v>10.2196</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.211</v>
+        <v>0.2182</v>
       </c>
       <c r="J125" t="n">
-        <v>6.119</v>
+        <v>6.3278</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.7829</v>
       </c>
       <c r="J126" t="n">
-        <v>-24.6007</v>
+        <v>-22.7041</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2927</v>
+        <v>0.2953</v>
       </c>
       <c r="J127" t="n">
-        <v>8.488300000000001</v>
+        <v>8.563700000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1667</v>
+        <v>0.1737</v>
       </c>
       <c r="J128" t="n">
-        <v>4.8343</v>
+        <v>5.0373</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1207</v>
+        <v>-0.1336</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.5003</v>
+        <v>-3.8744</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1318</v>
+        <v>-0.1451</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.8222</v>
+        <v>-4.2079</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1318</v>
+        <v>-0.1451</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.8222</v>
+        <v>-4.2079</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.41</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0286</v>
+        <v>0.9735</v>
       </c>
       <c r="J132" t="n">
-        <v>30.858</v>
+        <v>29.205</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9163</v>
+        <v>0.8593</v>
       </c>
       <c r="J133" t="n">
-        <v>27.489</v>
+        <v>25.779</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4169</v>
+        <v>0.4139</v>
       </c>
       <c r="J134" t="n">
-        <v>12.507</v>
+        <v>12.417</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0134</v>
+        <v>0.0312</v>
       </c>
       <c r="J135" t="n">
-        <v>0.402</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2433</v>
+        <v>-0.2323</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.299</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4483</v>
+        <v>0.4372</v>
       </c>
       <c r="J137" t="n">
-        <v>13.449</v>
+        <v>13.116</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2047</v>
+        <v>0.2069</v>
       </c>
       <c r="J138" t="n">
-        <v>6.141</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.448</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2296</v>
+        <v>-0.2451</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.888</v>
+        <v>-7.353</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4114</v>
+        <v>-0.4216</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.342</v>
+        <v>-12.648</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4408</v>
+        <v>1.4242</v>
       </c>
       <c r="J142" t="n">
-        <v>33.1384</v>
+        <v>32.7566</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.42</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0268</v>
+        <v>0.9751</v>
       </c>
       <c r="J143" t="n">
-        <v>23.6164</v>
+        <v>22.4273</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0113</v>
+        <v>0.9577</v>
       </c>
       <c r="J144" t="n">
-        <v>23.2599</v>
+        <v>22.0271</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.58</v>
+        <v>-0.5385</v>
       </c>
       <c r="J145" t="n">
-        <v>-13.34</v>
+        <v>-12.3855</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7105</v>
+        <v>-0.655</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.3415</v>
+        <v>-15.065</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.03</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1525</v>
+        <v>0.1442</v>
       </c>
       <c r="J147" t="n">
-        <v>3.5075</v>
+        <v>3.3166</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1348</v>
+        <v>-0.1529</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.1004</v>
+        <v>-3.5167</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.87</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1457</v>
+        <v>-0.1639</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.3511</v>
+        <v>-3.7697</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2541</v>
+        <v>-0.2724</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.8443</v>
+        <v>-6.2652</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5074</v>
+        <v>-0.5148</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.6702</v>
+        <v>-11.8404</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6798</v>
+        <v>0.658</v>
       </c>
       <c r="J152" t="n">
-        <v>20.394</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.34</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6631</v>
+        <v>0.6429</v>
       </c>
       <c r="J153" t="n">
-        <v>19.893</v>
+        <v>19.287</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0051</v>
+        <v>-0.0039</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.153</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1738</v>
+        <v>-0.1856</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.214</v>
+        <v>-5.568</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2952</v>
+        <v>-0.3063</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.856</v>
+        <v>-9.189</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.46</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1505</v>
+        <v>1.1025</v>
       </c>
       <c r="J157" t="n">
-        <v>34.515</v>
+        <v>33.075</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1304</v>
+        <v>-0.1357</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.912</v>
+        <v>-4.071</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.489</v>
+        <v>-0.4693</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.67</v>
+        <v>-14.079</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8</v>
+        <v>-0.7447</v>
       </c>
       <c r="J161" t="n">
-        <v>-24</v>
+        <v>-22.341</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.04</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2033</v>
+        <v>0.1884</v>
       </c>
       <c r="J162" t="n">
-        <v>4.6759</v>
+        <v>4.3332</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0402</v>
+        <v>-0.0585</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.9246</v>
+        <v>-1.3455</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.82</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1905</v>
+        <v>-0.2106</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.3815</v>
+        <v>-4.8438</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2108</v>
+        <v>-0.2307</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.8484</v>
+        <v>-5.3061</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.18</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7845</v>
+        <v>-0.772</v>
       </c>
       <c r="J166" t="n">
-        <v>-18.0435</v>
+        <v>-17.756</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.67</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3167</v>
+        <v>1.2978</v>
       </c>
       <c r="J167" t="n">
-        <v>30.2841</v>
+        <v>29.8494</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.44</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0354</v>
+        <v>0.9897</v>
       </c>
       <c r="J168" t="n">
-        <v>23.8142</v>
+        <v>22.7631</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8524</v>
+        <v>0.8107</v>
       </c>
       <c r="J169" t="n">
-        <v>19.6052</v>
+        <v>18.6461</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.16</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4294</v>
+        <v>0.4338</v>
       </c>
       <c r="J170" t="n">
-        <v>9.876200000000001</v>
+        <v>9.977399999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.15</v>
       </c>
       <c r="I171" t="n">
-        <v>0.4033</v>
+        <v>0.4102</v>
       </c>
       <c r="J171" t="n">
-        <v>9.2759</v>
+        <v>9.4346</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9885</v>
+        <v>0.9272</v>
       </c>
       <c r="J172" t="n">
-        <v>25.701</v>
+        <v>24.1072</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.14</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4222</v>
+        <v>0.4174</v>
       </c>
       <c r="J173" t="n">
-        <v>10.9772</v>
+        <v>10.8524</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.11</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3439</v>
+        <v>0.3453</v>
       </c>
       <c r="J174" t="n">
-        <v>8.9414</v>
+        <v>8.9778</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.08</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2594</v>
+        <v>0.2668</v>
       </c>
       <c r="J175" t="n">
-        <v>6.7444</v>
+        <v>6.9368</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1288</v>
+        <v>-0.1237</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.3488</v>
+        <v>-3.2162</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.11</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2902</v>
+        <v>0.2891</v>
       </c>
       <c r="J177" t="n">
-        <v>7.5452</v>
+        <v>7.5166</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.1216</v>
+        <v>-2.444</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1063</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.4232</v>
+        <v>-2.7638</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1685</v>
+        <v>-0.1839</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.381</v>
+        <v>-4.7814</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.77</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2593</v>
+        <v>-0.2744</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.7418</v>
+        <v>-7.1344</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.75</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4229</v>
+        <v>1.4084</v>
       </c>
       <c r="J182" t="n">
-        <v>32.7267</v>
+        <v>32.3932</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.069</v>
+        <v>1.0278</v>
       </c>
       <c r="J183" t="n">
-        <v>24.587</v>
+        <v>23.6394</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.34</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8586</v>
+        <v>0.8148</v>
       </c>
       <c r="J184" t="n">
-        <v>19.7478</v>
+        <v>18.7404</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2197</v>
+        <v>0.2392</v>
       </c>
       <c r="J185" t="n">
-        <v>5.0531</v>
+        <v>5.5016</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.9</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4285</v>
+        <v>-0.3977</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.855499999999999</v>
+        <v>-9.1471</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.89</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1177</v>
+        <v>-0.137</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.7071</v>
+        <v>-3.151</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2227</v>
+        <v>-0.242</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.1221</v>
+        <v>-5.566</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2227</v>
+        <v>-0.242</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.1221</v>
+        <v>-5.566</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2879</v>
+        <v>-0.3063</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.6217</v>
+        <v>-7.0449</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3257</v>
+        <v>-0.3429</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.4911</v>
+        <v>-7.8867</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.68</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8303</v>
+        <v>0.8142</v>
       </c>
       <c r="J192" t="n">
-        <v>21.5878</v>
+        <v>21.1692</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.39</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5107</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>13.2782</v>
+        <v>13.4576</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1715</v>
+        <v>0.1884</v>
       </c>
       <c r="J194" t="n">
-        <v>4.459</v>
+        <v>4.8984</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2147</v>
+        <v>-0.2247</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.5822</v>
+        <v>-5.8422</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3138</v>
+        <v>-0.3228</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.158799999999999</v>
+        <v>-8.392799999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7186</v>
+        <v>0.6899</v>
       </c>
       <c r="J197" t="n">
-        <v>18.6836</v>
+        <v>17.9374</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.96</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.058</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.508</v>
+        <v>-1.7836</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1698</v>
+        <v>-0.185</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.4148</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.71</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3189</v>
+        <v>-0.3323</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.291399999999999</v>
+        <v>-8.639799999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.67</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3569</v>
+        <v>-0.369</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.279400000000001</v>
+        <v>-9.593999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.28</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5657</v>
+        <v>0.5535</v>
       </c>
       <c r="J202" t="n">
-        <v>23.7594</v>
+        <v>23.247</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5483</v>
+        <v>0.5376</v>
       </c>
       <c r="J203" t="n">
-        <v>23.0286</v>
+        <v>22.5792</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0808</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.3936</v>
+        <v>-3.7758</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.87</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1723</v>
+        <v>-0.1844</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.2366</v>
+        <v>-7.7448</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.87</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1723</v>
+        <v>-0.1844</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.2366</v>
+        <v>-7.7448</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.999</v>
+        <v>0.929</v>
       </c>
       <c r="J207" t="n">
-        <v>41.958</v>
+        <v>39.018</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3726</v>
+        <v>0.3648</v>
       </c>
       <c r="J208" t="n">
-        <v>15.6492</v>
+        <v>15.3216</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.08</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2857</v>
+        <v>0.2846</v>
       </c>
       <c r="J209" t="n">
-        <v>11.9994</v>
+        <v>11.9532</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5464</v>
+        <v>-0.52</v>
       </c>
       <c r="J210" t="n">
-        <v>-22.9488</v>
+        <v>-21.84</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.9024</v>
+        <v>-0.8333</v>
       </c>
       <c r="J211" t="n">
-        <v>-37.9008</v>
+        <v>-34.9986</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.18</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4214</v>
+        <v>0.4138</v>
       </c>
       <c r="J212" t="n">
-        <v>12.642</v>
+        <v>12.414</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0488</v>
+        <v>0.0513</v>
       </c>
       <c r="J213" t="n">
-        <v>1.464</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0712</v>
+        <v>-0.0825</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.136</v>
+        <v>-2.475</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1812</v>
+        <v>-0.1962</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.436</v>
+        <v>-5.886</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3103</v>
+        <v>-0.3238</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.308999999999999</v>
+        <v>-9.714</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9287</v>
+        <v>0.8605</v>
       </c>
       <c r="J217" t="n">
-        <v>27.861</v>
+        <v>25.815</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5556</v>
+        <v>0.5316</v>
       </c>
       <c r="J218" t="n">
-        <v>16.668</v>
+        <v>15.948</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0882</v>
+        <v>0.0959</v>
       </c>
       <c r="J219" t="n">
-        <v>2.646</v>
+        <v>2.877</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5249</v>
+        <v>-0.4998</v>
       </c>
       <c r="J220" t="n">
-        <v>-15.747</v>
+        <v>-14.994</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6566</v>
+        <v>-0.6171</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.698</v>
+        <v>-18.513</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2962</v>
+        <v>0.2979</v>
       </c>
       <c r="J222" t="n">
-        <v>8.2936</v>
+        <v>8.341200000000001</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.08</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2135</v>
+        <v>0.2186</v>
       </c>
       <c r="J223" t="n">
-        <v>5.978</v>
+        <v>6.1208</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0182</v>
+        <v>-0.0235</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0728</v>
+        <v>-0.0837</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.0384</v>
+        <v>-2.3436</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3418</v>
+        <v>-0.3538</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.570399999999999</v>
+        <v>-9.9064</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1358</v>
+        <v>1.0944</v>
       </c>
       <c r="J227" t="n">
-        <v>31.8024</v>
+        <v>30.6432</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.24</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6743</v>
+        <v>0.6435</v>
       </c>
       <c r="J228" t="n">
-        <v>18.8804</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1381</v>
+        <v>0.1509</v>
       </c>
       <c r="J229" t="n">
-        <v>3.8668</v>
+        <v>4.2252</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1973</v>
+        <v>-0.1916</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.5244</v>
+        <v>-5.3648</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3838</v>
+        <v>-0.3663</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.7464</v>
+        <v>-10.2564</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.78</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2132</v>
+        <v>-0.2367</v>
       </c>
       <c r="J232" t="n">
-        <v>-4.6904</v>
+        <v>-5.2074</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.75</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2441</v>
+        <v>-0.2668</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.3702</v>
+        <v>-5.8696</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.7</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2931</v>
+        <v>-0.3142</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.4482</v>
+        <v>-6.9124</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3025</v>
+        <v>-0.3233</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.655</v>
+        <v>-7.1126</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.41</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5617</v>
+        <v>-0.5683</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.3574</v>
+        <v>-12.5026</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6178</v>
+        <v>1.621</v>
       </c>
       <c r="J237" t="n">
-        <v>35.5916</v>
+        <v>35.662</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.66</v>
       </c>
       <c r="I238" t="n">
-        <v>1.2784</v>
+        <v>1.262</v>
       </c>
       <c r="J238" t="n">
-        <v>28.1248</v>
+        <v>27.764</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.4</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9518</v>
+        <v>0.9055</v>
       </c>
       <c r="J239" t="n">
-        <v>20.9396</v>
+        <v>19.921</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.27</v>
       </c>
       <c r="I240" t="n">
-        <v>0.6663</v>
+        <v>0.652</v>
       </c>
       <c r="J240" t="n">
-        <v>14.6586</v>
+        <v>14.344</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.23</v>
       </c>
       <c r="I241" t="n">
-        <v>0.5716</v>
+        <v>0.5679</v>
       </c>
       <c r="J241" t="n">
-        <v>12.5752</v>
+        <v>12.4938</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.464</v>
+        <v>0.4487</v>
       </c>
       <c r="J242" t="n">
-        <v>10.672</v>
+        <v>10.3201</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0643</v>
+        <v>0.0625</v>
       </c>
       <c r="J243" t="n">
-        <v>1.4789</v>
+        <v>1.4375</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1233</v>
+        <v>-0.1386</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.8359</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.7</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3224</v>
+        <v>-0.3368</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.4152</v>
+        <v>-7.7464</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.63</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3884</v>
+        <v>-0.4003</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.933199999999999</v>
+        <v>-9.206899999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.47</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0854</v>
+        <v>1.0462</v>
       </c>
       <c r="J247" t="n">
-        <v>24.9642</v>
+        <v>24.0626</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.39</v>
       </c>
       <c r="I248" t="n">
-        <v>0.967</v>
+        <v>0.9132</v>
       </c>
       <c r="J248" t="n">
-        <v>22.241</v>
+        <v>21.0036</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.36</v>
       </c>
       <c r="I249" t="n">
-        <v>0.9065</v>
+        <v>0.8563</v>
       </c>
       <c r="J249" t="n">
-        <v>20.8495</v>
+        <v>19.6949</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.25</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6412</v>
       </c>
       <c r="J250" t="n">
-        <v>15.2674</v>
+        <v>14.7476</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.95</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2708</v>
+        <v>-0.2516</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.2284</v>
+        <v>-5.7868</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>2.08</v>
       </c>
       <c r="I252" t="n">
-        <v>1.7213</v>
+        <v>1.7338</v>
       </c>
       <c r="J252" t="n">
-        <v>32.7047</v>
+        <v>32.9422</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.79</v>
       </c>
       <c r="I253" t="n">
-        <v>1.4066</v>
+        <v>1.4022</v>
       </c>
       <c r="J253" t="n">
-        <v>26.7254</v>
+        <v>26.6418</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.55</v>
       </c>
       <c r="I254" t="n">
-        <v>1.1404</v>
+        <v>1.116</v>
       </c>
       <c r="J254" t="n">
-        <v>21.6676</v>
+        <v>21.204</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.43</v>
       </c>
       <c r="I255" t="n">
-        <v>0.9845</v>
+        <v>0.9423</v>
       </c>
       <c r="J255" t="n">
-        <v>18.7055</v>
+        <v>17.9037</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.36</v>
       </c>
       <c r="I256" t="n">
-        <v>0.8429</v>
+        <v>0.8123</v>
       </c>
       <c r="J256" t="n">
-        <v>16.0151</v>
+        <v>15.4337</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.68</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2578</v>
+        <v>-0.2901</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.8982</v>
+        <v>-5.5119</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.54</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.4063</v>
+        <v>-0.4288</v>
       </c>
       <c r="J258" t="n">
-        <v>-7.7197</v>
+        <v>-8.1472</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.52</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4256</v>
+        <v>-0.4468</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.086399999999999</v>
+        <v>-8.4892</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.41</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5262</v>
+        <v>-0.5405</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.9978</v>
+        <v>-10.2695</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.28</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.6586</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.4583</v>
+        <v>-12.5134</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4083/event_4083_evp_summary.xlsx
+++ b/database/event/4083/event_4083_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6268</v>
+        <v>5.604</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0763</v>
+        <v>2.0679</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9372</v>
+        <v>1.9471</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6268</v>
+        <v>5.604</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0836</v>
+        <v>3.0745</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5432</v>
+        <v>2.5295</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2797</v>
+        <v>5.1006</v>
       </c>
       <c r="I2" t="n">
-        <v>2.851</v>
+        <v>2.8638</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5432</v>
+        <v>2.5295</v>
       </c>
       <c r="K2" t="n">
         <v>176</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3942</v>
+        <v>5.3933</v>
       </c>
       <c r="N2" t="n">
         <v>319</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2419</v>
+        <v>5.2656</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9343</v>
+        <v>1.9431</v>
       </c>
       <c r="D3" t="n">
-        <v>1.762</v>
+        <v>1.7929</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2419</v>
+        <v>5.2656</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3641</v>
+        <v>2.4918</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8778</v>
+        <v>2.7738</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9058</v>
+        <v>2.9125</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5691</v>
+        <v>1.6353</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8778</v>
+        <v>2.7738</v>
       </c>
       <c r="K3" t="n">
         <v>176</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4469</v>
+        <v>4.4091</v>
       </c>
       <c r="N3" t="n">
         <v>319</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8811</v>
+        <v>4.9486</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8012</v>
+        <v>1.8261</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5978</v>
+        <v>1.6485</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8811</v>
+        <v>4.9486</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2253</v>
+        <v>2.2883</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6558</v>
+        <v>2.6603</v>
       </c>
       <c r="H4" t="n">
-        <v>2.448</v>
+        <v>2.2883</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3219</v>
+        <v>1.2848</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6558</v>
+        <v>2.6603</v>
       </c>
       <c r="K4" t="n">
         <v>121</v>
@@ -621,7 +621,7 @@
         <v>139</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9777</v>
+        <v>3.9451</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3108</v>
+        <v>4.3262</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5907</v>
+        <v>1.5964</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3382</v>
+        <v>1.365</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3108</v>
+        <v>4.3262</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3081</v>
+        <v>2.4198</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0027</v>
+        <v>1.9064</v>
       </c>
       <c r="H5" t="n">
-        <v>2.721</v>
+        <v>2.6425</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4693</v>
+        <v>1.4837</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0027</v>
+        <v>1.9064</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.472</v>
+        <v>3.3901</v>
       </c>
       <c r="N5" t="n">
         <v>260</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1281</v>
+        <v>4.0466</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5233</v>
+        <v>1.4932</v>
       </c>
       <c r="D6" t="n">
-        <v>1.255</v>
+        <v>1.2376</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1281</v>
+        <v>4.0466</v>
       </c>
       <c r="F6" t="n">
-        <v>2.574</v>
+        <v>2.5889</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5541</v>
+        <v>1.4577</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5984</v>
+        <v>3.2773</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9431</v>
+        <v>1.8401</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5541</v>
+        <v>1.4577</v>
       </c>
       <c r="K6" t="n">
         <v>176</v>
@@ -713,7 +713,7 @@
         <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4972</v>
+        <v>3.2978</v>
       </c>
       <c r="N6" t="n">
         <v>319</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0391</v>
+        <v>3.958</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4905</v>
+        <v>1.4605</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2145</v>
+        <v>1.1973</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0391</v>
+        <v>3.958</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6458</v>
+        <v>2.6571</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3933</v>
+        <v>1.3009</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8354</v>
+        <v>3.5334</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0711</v>
+        <v>1.9839</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3933</v>
+        <v>1.3009</v>
       </c>
       <c r="K7" t="n">
         <v>176</v>
@@ -759,7 +759,7 @@
         <v>143</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4644</v>
+        <v>3.2848</v>
       </c>
       <c r="N7" t="n">
         <v>319</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5745</v>
+        <v>3.49</v>
       </c>
       <c r="C8" t="n">
-        <v>1.319</v>
+        <v>1.2878</v>
       </c>
       <c r="D8" t="n">
-        <v>1.003</v>
+        <v>0.9841</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5745</v>
+        <v>3.49</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8229</v>
+        <v>2.842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7516</v>
+        <v>0.648</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4197</v>
+        <v>4.2273</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3866</v>
+        <v>2.3735</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7516</v>
+        <v>0.648</v>
       </c>
       <c r="K8" t="n">
         <v>175</v>
@@ -805,7 +805,7 @@
         <v>67</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1382</v>
+        <v>3.0215</v>
       </c>
       <c r="N8" t="n">
         <v>242</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4841</v>
+        <v>3.3912</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2857</v>
+        <v>1.2514</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9618</v>
+        <v>0.9391</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4841</v>
+        <v>3.3912</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1972</v>
+        <v>2.0238</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2869</v>
+        <v>1.3674</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3552</v>
+        <v>2.0238</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2718</v>
+        <v>1.1363</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2869</v>
+        <v>1.3674</v>
       </c>
       <c r="K9" t="n">
         <v>176</v>
@@ -851,7 +851,7 @@
         <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5587</v>
+        <v>2.5037</v>
       </c>
       <c r="N9" t="n">
         <v>319</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2551</v>
+        <v>3.1788</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2012</v>
+        <v>1.173</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8576</v>
+        <v>0.8423</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2551</v>
+        <v>3.1788</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3775</v>
+        <v>3.3314</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1224</v>
+        <v>-0.1526</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2495</v>
+        <v>6.0648</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3747</v>
+        <v>3.4052</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1224</v>
+        <v>-0.1526</v>
       </c>
       <c r="K10" t="n">
         <v>71</v>
@@ -897,7 +897,7 @@
         <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2523</v>
+        <v>3.2526</v>
       </c>
       <c r="N10" t="n">
         <v>142</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4383</v>
+        <v>2.4013</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8998</v>
+        <v>0.8861</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4858</v>
+        <v>0.4881</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4383</v>
+        <v>2.4013</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4383</v>
+        <v>2.4013</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6117</v>
+        <v>2.553</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6117</v>
+        <v>2.553</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6117</v>
+        <v>2.553</v>
       </c>
       <c r="N11" t="n">
         <v>135</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.427</v>
+        <v>2.3343</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8956</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4806</v>
+        <v>0.4576</v>
       </c>
       <c r="E12" t="n">
-        <v>2.427</v>
+        <v>2.3343</v>
       </c>
       <c r="F12" t="n">
-        <v>2.427</v>
+        <v>2.8425</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.5082</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5871</v>
+        <v>4.2293</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5871</v>
+        <v>2.3746</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.5082</v>
       </c>
       <c r="K12" t="n">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5871</v>
+        <v>1.8664</v>
       </c>
       <c r="N12" t="n">
-        <v>173</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3024</v>
+        <v>2.3301</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8496</v>
+        <v>0.8598</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4239</v>
+        <v>0.4557</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3024</v>
+        <v>2.3301</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8413</v>
+        <v>2.3301</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5389</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4803</v>
+        <v>2.3898</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4193</v>
+        <v>2.3898</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5389</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="L13" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8804</v>
+        <v>2.3898</v>
       </c>
       <c r="N13" t="n">
-        <v>260</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2448</v>
+        <v>2.2508</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8284</v>
+        <v>0.8306</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3977</v>
+        <v>0.4196</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2448</v>
+        <v>2.2508</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5602</v>
+        <v>2.6038</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3154</v>
+        <v>-0.353</v>
       </c>
       <c r="H14" t="n">
-        <v>3.553</v>
+        <v>3.333</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9186</v>
+        <v>1.8714</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3154</v>
+        <v>-0.353</v>
       </c>
       <c r="K14" t="n">
         <v>71</v>
@@ -1081,7 +1081,7 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6032</v>
+        <v>1.5184</v>
       </c>
       <c r="N14" t="n">
         <v>142</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0419</v>
+        <v>2.0893</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3053</v>
+        <v>0.346</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0419</v>
+        <v>2.0893</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3608</v>
+        <v>2.4446</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3189</v>
+        <v>-0.3553</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8949</v>
+        <v>2.7353</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5632</v>
+        <v>1.5358</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3189</v>
+        <v>-0.3553</v>
       </c>
       <c r="K15" t="n">
         <v>175</v>
@@ -1127,7 +1127,7 @@
         <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2443</v>
+        <v>1.1805</v>
       </c>
       <c r="N15" t="n">
         <v>242</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9559</v>
+        <v>2.0299</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7217</v>
+        <v>0.7491</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2662</v>
+        <v>0.3189</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9559</v>
+        <v>2.0299</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3795</v>
+        <v>2.476</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4236</v>
+        <v>-0.4461</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9567</v>
+        <v>2.8532</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5966</v>
+        <v>1.602</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4236</v>
+        <v>-0.4461</v>
       </c>
       <c r="K16" t="n">
         <v>71</v>
@@ -1173,7 +1173,7 @@
         <v>71</v>
       </c>
       <c r="M16" t="n">
-        <v>1.173</v>
+        <v>1.1559</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9466</v>
+        <v>1.9374</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7183</v>
+        <v>0.7149</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2619</v>
+        <v>0.2768</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9466</v>
+        <v>1.9374</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9466</v>
+        <v>2.9374</v>
       </c>
       <c r="G17" t="n">
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8279</v>
+        <v>4.5857</v>
       </c>
       <c r="I17" t="n">
-        <v>2.607</v>
+        <v>2.5747</v>
       </c>
       <c r="J17" t="n">
         <v>-1</v>
@@ -1219,7 +1219,7 @@
         <v>71</v>
       </c>
       <c r="M17" t="n">
-        <v>1.607</v>
+        <v>1.5747</v>
       </c>
       <c r="N17" t="n">
         <v>142</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4983</v>
+        <v>1.4987</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0579</v>
+        <v>0.0769</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4983</v>
+        <v>1.4987</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4983</v>
+        <v>1.4987</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4983</v>
+        <v>1.4987</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4983</v>
+        <v>1.4987</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4983</v>
+        <v>1.4987</v>
       </c>
       <c r="N18" t="n">
         <v>173</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3156</v>
+        <v>1.1226</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4855</v>
+        <v>0.4142</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0253</v>
+        <v>-0.0944</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3156</v>
+        <v>1.1226</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7163</v>
+        <v>0.6091</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5135</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7163</v>
+        <v>0.6091</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3868</v>
+        <v>0.342</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5135</v>
       </c>
       <c r="K19" t="n">
         <v>175</v>
@@ -1311,7 +1311,7 @@
         <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9861</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>242</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0073</v>
+        <v>1.0954</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3717</v>
+        <v>0.4042</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1657</v>
+        <v>-0.1068</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0073</v>
+        <v>1.0954</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3845</v>
+        <v>-1.2072</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3918</v>
+        <v>2.3026</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3845</v>
+        <v>-1.2072</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7476</v>
+        <v>-0.6778</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3918</v>
+        <v>2.3026</v>
       </c>
       <c r="K20" t="n">
         <v>121</v>
@@ -1357,7 +1357,7 @@
         <v>139</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6442</v>
+        <v>1.6248</v>
       </c>
       <c r="N20" t="n">
         <v>260</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7922</v>
+        <v>0.781</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2923</v>
+        <v>0.2882</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2636</v>
+        <v>-0.25</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7922</v>
+        <v>0.781</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7922</v>
+        <v>0.781</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7922</v>
+        <v>0.781</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7922</v>
+        <v>0.781</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7922</v>
+        <v>0.781</v>
       </c>
       <c r="N21" t="n">
         <v>135</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5858</v>
+        <v>0.5174</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2162</v>
+        <v>0.1909</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3575</v>
+        <v>-0.3701</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5858</v>
+        <v>0.5174</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8093</v>
+        <v>0.7418</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2235</v>
+        <v>-0.2244</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8093</v>
+        <v>0.7418</v>
       </c>
       <c r="I22" t="n">
-        <v>0.437</v>
+        <v>0.4165</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2235</v>
+        <v>-0.2244</v>
       </c>
       <c r="K22" t="n">
         <v>71</v>
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2135</v>
+        <v>0.1921</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5563</v>
+        <v>0.4754</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2053</v>
+        <v>0.1754</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.371</v>
+        <v>-0.3892</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5563</v>
+        <v>0.4754</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5563</v>
+        <v>0.4754</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5563</v>
+        <v>0.4754</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5563</v>
+        <v>0.4754</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5563</v>
+        <v>0.4754</v>
       </c>
       <c r="N23" t="n">
         <v>72</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4564</v>
+        <v>0.4123</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1684</v>
+        <v>0.1521</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4164</v>
+        <v>-0.418</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4564</v>
+        <v>0.4123</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4564</v>
+        <v>0.4123</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4564</v>
+        <v>0.4123</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4564</v>
+        <v>0.4123</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4564</v>
+        <v>0.4123</v>
       </c>
       <c r="N24" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3807</v>
+        <v>0.3557</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1405</v>
+        <v>0.1313</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4509</v>
+        <v>-0.4437</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3807</v>
+        <v>0.3557</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3807</v>
+        <v>0.3557</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3807</v>
+        <v>0.3557</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3807</v>
+        <v>0.3557</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3807</v>
+        <v>0.3557</v>
       </c>
       <c r="N25" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2608</v>
+        <v>0.2974</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1097</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.4703</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2608</v>
+        <v>0.2974</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2608</v>
+        <v>0.2974</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2608</v>
+        <v>0.2974</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2608</v>
+        <v>0.2974</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2608</v>
+        <v>0.2974</v>
       </c>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2578</v>
+        <v>0.225</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0951</v>
+        <v>0.083</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5068</v>
+        <v>-0.5033</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2578</v>
+        <v>0.225</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2578</v>
+        <v>0.225</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2578</v>
+        <v>0.225</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2578</v>
+        <v>0.225</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2578</v>
+        <v>0.225</v>
       </c>
       <c r="N27" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2324</v>
+        <v>0.1557</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0858</v>
+        <v>0.0575</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5184</v>
+        <v>-0.5349</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2324</v>
+        <v>0.1557</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2324</v>
+        <v>0.1557</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2324</v>
+        <v>0.1557</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2324</v>
+        <v>0.1557</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2324</v>
+        <v>0.1557</v>
       </c>
       <c r="N28" t="n">
         <v>81</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0219</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0081</v>
+        <v>0.0299</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6142</v>
+        <v>-0.5688</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0219</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0219</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0219</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0219</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0219</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>173</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0145</v>
+        <v>-0.0596</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0054</v>
+        <v>-0.022</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6308</v>
+        <v>-0.6329</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0145</v>
+        <v>-0.0596</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0145</v>
+        <v>-0.0596</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0145</v>
+        <v>-0.0596</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0145</v>
+        <v>-0.0596</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0145</v>
+        <v>-0.0596</v>
       </c>
       <c r="N30" t="n">
         <v>72</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1904</v>
+        <v>-0.199</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0703</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7109</v>
+        <v>-0.6964</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1904</v>
+        <v>-0.199</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1904</v>
+        <v>-0.199</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1904</v>
+        <v>-0.199</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1904</v>
+        <v>-0.199</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1904</v>
+        <v>-0.199</v>
       </c>
       <c r="N31" t="n">
         <v>81</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4844</v>
+        <v>-0.4912</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1787</v>
+        <v>-0.1813</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8447</v>
+        <v>-0.8296</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4844</v>
+        <v>-0.4912</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2478</v>
+        <v>0.2647</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7322</v>
+        <v>-0.7559</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2478</v>
+        <v>0.2647</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1338</v>
+        <v>0.1486</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7322</v>
+        <v>-0.7559</v>
       </c>
       <c r="K32" t="n">
         <v>175</v>
@@ -1909,7 +1909,7 @@
         <v>67</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5983999999999999</v>
+        <v>-0.6073</v>
       </c>
       <c r="N32" t="n">
         <v>242</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5878</v>
+        <v>-0.5274</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2169</v>
+        <v>-0.1946</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8918</v>
+        <v>-0.846</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5878</v>
+        <v>-0.5274</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5878</v>
+        <v>-0.5274</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5878</v>
+        <v>-0.5274</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5878</v>
+        <v>-0.5274</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5878</v>
+        <v>-0.5274</v>
       </c>
       <c r="N33" t="n">
         <v>135</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6312</v>
+        <v>-0.6377</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2329</v>
+        <v>-0.2353</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9115</v>
+        <v>-0.8963</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6312</v>
+        <v>-0.6377</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6312</v>
+        <v>-0.6377</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6312</v>
+        <v>-0.6377</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6312</v>
+        <v>-0.6377</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6312</v>
+        <v>-0.6377</v>
       </c>
       <c r="N34" t="n">
         <v>81</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6925</v>
+        <v>-0.664</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2555</v>
+        <v>-0.245</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9394</v>
+        <v>-0.9083</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6925</v>
+        <v>-0.664</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6925</v>
+        <v>-0.664</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6925</v>
+        <v>-0.664</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6925</v>
+        <v>-0.664</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6925</v>
+        <v>-0.664</v>
       </c>
       <c r="N35" t="n">
         <v>81</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7751</v>
+        <v>-0.7609</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.286</v>
+        <v>-0.2808</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.977</v>
+        <v>-0.9524</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7751</v>
+        <v>-0.7609</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7751</v>
+        <v>-0.7609</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7751</v>
+        <v>-0.7609</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7751</v>
+        <v>-0.7609</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7751</v>
+        <v>-0.7609</v>
       </c>
       <c r="N36" t="n">
         <v>72</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7936</v>
+        <v>-0.7623</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2928</v>
+        <v>-0.2813</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9855</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7936</v>
+        <v>-0.7623</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7936</v>
+        <v>-0.7623</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7936</v>
+        <v>-0.7623</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7936</v>
+        <v>-0.7623</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7936</v>
+        <v>-0.7623</v>
       </c>
       <c r="N37" t="n">
         <v>72</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0122</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3735</v>
+        <v>-0.3458</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.085</v>
+        <v>-1.0326</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0122</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0122</v>
+        <v>-0.8113</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.1257</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0122</v>
+        <v>-0.8113</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0122</v>
+        <v>-0.4555</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.1257</v>
       </c>
       <c r="K38" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0122</v>
+        <v>-0.5812</v>
       </c>
       <c r="N38" t="n">
-        <v>173</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0832</v>
+        <v>-1.0387</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3997</v>
+        <v>-0.3833</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1173</v>
+        <v>-1.079</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0832</v>
+        <v>-1.0387</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0409</v>
+        <v>-1.0387</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0423</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0409</v>
+        <v>-1.0387</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5621</v>
+        <v>-1.0387</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.0423</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L39" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.6044</v>
+        <v>-1.0387</v>
       </c>
       <c r="N39" t="n">
-        <v>242</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6162</v>
+        <v>-1.6647</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5964</v>
+        <v>-0.6143</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3599</v>
+        <v>-1.3641</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6162</v>
+        <v>-1.6647</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6162</v>
+        <v>-1.6647</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6162</v>
+        <v>-1.6647</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6162</v>
+        <v>-1.6647</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6162</v>
+        <v>-1.6647</v>
       </c>
       <c r="N40" t="n">
         <v>72</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9038</v>
+        <v>-1.7345</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7025</v>
+        <v>-0.64</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4909</v>
+        <v>-1.3959</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9038</v>
+        <v>-1.7345</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7156</v>
+        <v>-1.5451</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1882</v>
+        <v>-0.1894</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7156</v>
+        <v>-1.5451</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9264</v>
+        <v>-0.8675</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1882</v>
+        <v>-0.1894</v>
       </c>
       <c r="K41" t="n">
         <v>121</v>
@@ -2323,7 +2323,7 @@
         <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1146</v>
+        <v>-1.0569</v>
       </c>
       <c r="N41" t="n">
         <v>260</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3603</v>
+        <v>0.3189</v>
       </c>
       <c r="J2" t="n">
-        <v>10.809</v>
+        <v>9.567</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3343</v>
+        <v>0.2937</v>
       </c>
       <c r="J3" t="n">
-        <v>10.029</v>
+        <v>8.811</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0956</v>
+        <v>0.0747</v>
       </c>
       <c r="J4" t="n">
-        <v>2.868</v>
+        <v>2.241</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0024</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.132</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2368</v>
+        <v>-0.1989</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.104</v>
+        <v>-5.967</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9401</v>
+        <v>0.8941</v>
       </c>
       <c r="J7" t="n">
-        <v>28.203</v>
+        <v>26.823</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.116</v>
+        <v>0.0896</v>
       </c>
       <c r="J8" t="n">
-        <v>3.48</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0313</v>
+        <v>-0.0225</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.675</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0793</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.379</v>
+        <v>-1.911</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1656</v>
+        <v>-0.1453</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.968</v>
+        <v>-4.359</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6448</v>
+        <v>0.6095</v>
       </c>
       <c r="J12" t="n">
-        <v>27.0816</v>
+        <v>25.599</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6014</v>
+        <v>0.5645</v>
       </c>
       <c r="J13" t="n">
-        <v>25.2588</v>
+        <v>23.709</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4196</v>
+        <v>0.381</v>
       </c>
       <c r="J14" t="n">
-        <v>17.6232</v>
+        <v>16.002</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2698</v>
+        <v>0.2361</v>
       </c>
       <c r="J15" t="n">
-        <v>11.3316</v>
+        <v>9.9162</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3382</v>
+        <v>-0.2962</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.2044</v>
+        <v>-12.4404</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="J17" t="n">
-        <v>24.3642</v>
+        <v>21.8484</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.223</v>
+        <v>0.1814</v>
       </c>
       <c r="J18" t="n">
-        <v>9.366</v>
+        <v>7.6188</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2034</v>
+        <v>0.1641</v>
       </c>
       <c r="J19" t="n">
-        <v>8.5428</v>
+        <v>6.8922</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0299</v>
+        <v>-0.0213</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2558</v>
+        <v>-0.8946</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1752</v>
+        <v>-0.1547</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.3584</v>
+        <v>-6.4974</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.25</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7952</v>
+        <v>1.8427</v>
       </c>
       <c r="J22" t="n">
-        <v>32.3136</v>
+        <v>33.1686</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.67</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1224</v>
+        <v>1.1186</v>
       </c>
       <c r="J23" t="n">
-        <v>20.2032</v>
+        <v>20.1348</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.52</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9383</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>16.8894</v>
+        <v>16.776</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.23</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5301</v>
+        <v>0.5281</v>
       </c>
       <c r="J25" t="n">
-        <v>9.5418</v>
+        <v>9.505800000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1168</v>
+        <v>0.0858</v>
       </c>
       <c r="J26" t="n">
-        <v>2.1024</v>
+        <v>1.5444</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2313</v>
+        <v>0.2215</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1634</v>
+        <v>3.987</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.66</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3455</v>
+        <v>-0.3352</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.219</v>
+        <v>-6.0336</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.6</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3967</v>
+        <v>-0.3875</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.1406</v>
+        <v>-6.975</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.49</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.493</v>
+        <v>-0.4904</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.874000000000001</v>
+        <v>-8.827199999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.36</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6073</v>
+        <v>-0.6202</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.9314</v>
+        <v>-11.1636</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3303</v>
+        <v>0.3241</v>
       </c>
       <c r="J32" t="n">
-        <v>7.9272</v>
+        <v>7.7784</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1574</v>
+        <v>0.1414</v>
       </c>
       <c r="J33" t="n">
-        <v>3.7776</v>
+        <v>3.3936</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2194</v>
+        <v>-0.2004</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.2656</v>
+        <v>-4.8096</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3062</v>
+        <v>-0.2886</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.3488</v>
+        <v>-6.9264</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.52</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4943</v>
+        <v>-0.4933</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.8632</v>
+        <v>-11.8392</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7508</v>
+        <v>0.702</v>
       </c>
       <c r="J37" t="n">
-        <v>18.0192</v>
+        <v>16.848</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4051</v>
+        <v>0.3456</v>
       </c>
       <c r="J38" t="n">
-        <v>9.7224</v>
+        <v>8.2944</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.2</v>
       </c>
       <c r="I39" t="n">
-        <v>0.292</v>
+        <v>0.2424</v>
       </c>
       <c r="J39" t="n">
-        <v>7.008</v>
+        <v>5.8176</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.255</v>
+        <v>0.2091</v>
       </c>
       <c r="J40" t="n">
-        <v>6.12</v>
+        <v>5.0184</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.08</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1316</v>
+        <v>0.1011</v>
       </c>
       <c r="J41" t="n">
-        <v>3.1584</v>
+        <v>2.4264</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6019</v>
+        <v>0.5889</v>
       </c>
       <c r="J42" t="n">
-        <v>15.0475</v>
+        <v>14.7225</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.536</v>
+        <v>0.5239</v>
       </c>
       <c r="J43" t="n">
-        <v>13.4</v>
+        <v>13.0975</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.13</v>
       </c>
       <c r="I44" t="n">
-        <v>0.405</v>
+        <v>0.3641</v>
       </c>
       <c r="J44" t="n">
-        <v>10.125</v>
+        <v>9.102499999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0054</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.2175</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7563</v>
+        <v>-0.7285</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.9075</v>
+        <v>-18.2125</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2653</v>
+        <v>0.2174</v>
       </c>
       <c r="J47" t="n">
-        <v>6.6325</v>
+        <v>5.435</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2452</v>
+        <v>0.199</v>
       </c>
       <c r="J48" t="n">
-        <v>6.13</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1587</v>
+        <v>0.1223</v>
       </c>
       <c r="J49" t="n">
-        <v>3.9675</v>
+        <v>3.0575</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.79</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2565</v>
+        <v>-0.2368</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.4125</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.66</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3785</v>
+        <v>-0.3657</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.4625</v>
+        <v>-9.1425</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.93</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0911</v>
+        <v>-0.0775</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.0953</v>
+        <v>-1.7825</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1037</v>
+        <v>-0.0896</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.3851</v>
+        <v>-2.0608</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2142</v>
+        <v>-0.1974</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.9266</v>
+        <v>-4.5402</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3448</v>
+        <v>-0.3296</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.9304</v>
+        <v>-7.5808</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.6</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4168</v>
+        <v>-0.4067</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.586399999999999</v>
+        <v>-9.354100000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.57</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0282</v>
+        <v>1.017</v>
       </c>
       <c r="J57" t="n">
-        <v>23.6486</v>
+        <v>23.391</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.43</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8409</v>
+        <v>0.8276</v>
       </c>
       <c r="J58" t="n">
-        <v>19.3407</v>
+        <v>19.0348</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.37</v>
       </c>
       <c r="I59" t="n">
-        <v>0.758</v>
+        <v>0.746</v>
       </c>
       <c r="J59" t="n">
-        <v>17.434</v>
+        <v>17.158</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3918</v>
+        <v>0.3599</v>
       </c>
       <c r="J60" t="n">
-        <v>9.0114</v>
+        <v>8.277699999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2094</v>
+        <v>0.1802</v>
       </c>
       <c r="J61" t="n">
-        <v>4.8162</v>
+        <v>4.1446</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3563</v>
+        <v>0.2962</v>
       </c>
       <c r="J62" t="n">
-        <v>9.620100000000001</v>
+        <v>7.9974</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2956</v>
+        <v>0.2411</v>
       </c>
       <c r="J63" t="n">
-        <v>7.9812</v>
+        <v>6.5097</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2318</v>
+        <v>0.1848</v>
       </c>
       <c r="J64" t="n">
-        <v>6.2586</v>
+        <v>4.9896</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1188</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>3.2076</v>
+        <v>2.4138</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1994</v>
+        <v>-0.1789</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.3838</v>
+        <v>-4.8303</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5023</v>
+        <v>0.5308</v>
       </c>
       <c r="J67" t="n">
-        <v>13.5621</v>
+        <v>14.3316</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.037</v>
+        <v>0.0277</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999</v>
+        <v>0.7479</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.109</v>
+        <v>-0.0919</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.943</v>
+        <v>-2.4813</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.8934</v>
+        <v>-3.375</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3812</v>
+        <v>-0.3689</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.2924</v>
+        <v>-9.9603</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.77</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.2386</v>
+        <v>-0.2242</v>
       </c>
       <c r="J72" t="n">
-        <v>-5.0106</v>
+        <v>-4.7082</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.77</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2386</v>
+        <v>-0.2242</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.0106</v>
+        <v>-4.7082</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3269</v>
+        <v>-0.3162</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.8649</v>
+        <v>-6.6402</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.53</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4575</v>
+        <v>-0.4518</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.6075</v>
+        <v>-9.4878</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.38</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5895</v>
+        <v>-0.5994</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.3795</v>
+        <v>-12.5874</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.91</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4152</v>
+        <v>1.4258</v>
       </c>
       <c r="J77" t="n">
-        <v>29.7192</v>
+        <v>29.9418</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.63</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0777</v>
+        <v>1.0717</v>
       </c>
       <c r="J78" t="n">
-        <v>22.6317</v>
+        <v>22.5057</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.55</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9779</v>
+        <v>0.9705</v>
       </c>
       <c r="J79" t="n">
-        <v>20.5359</v>
+        <v>20.3805</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6998</v>
+        <v>0.6947</v>
       </c>
       <c r="J80" t="n">
-        <v>14.6958</v>
+        <v>14.5887</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.09</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2366</v>
+        <v>0.203</v>
       </c>
       <c r="J81" t="n">
-        <v>4.9686</v>
+        <v>4.263</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4317</v>
+        <v>1.4673</v>
       </c>
       <c r="J82" t="n">
-        <v>42.951</v>
+        <v>44.019</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.04</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1559</v>
+        <v>0.1297</v>
       </c>
       <c r="J83" t="n">
-        <v>4.677</v>
+        <v>3.891</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0862</v>
+        <v>0.0682</v>
       </c>
       <c r="J84" t="n">
-        <v>2.586</v>
+        <v>2.046</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.89</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3869</v>
+        <v>-0.3441</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.607</v>
+        <v>-10.323</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.569</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.192</v>
+        <v>-17.07</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.47</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.7796</v>
       </c>
       <c r="J87" t="n">
-        <v>24.966</v>
+        <v>23.388</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.17</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3684</v>
+        <v>0.3144</v>
       </c>
       <c r="J88" t="n">
-        <v>11.052</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0045</v>
+        <v>-0.0029</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.135</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.88</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1754</v>
+        <v>-0.1549</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.262</v>
+        <v>-4.647</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.83</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2284</v>
+        <v>-0.2081</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.852</v>
+        <v>-6.243</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2939</v>
+        <v>0.2815</v>
       </c>
       <c r="J92" t="n">
-        <v>12.0499</v>
+        <v>11.5415</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1783</v>
+        <v>0.162</v>
       </c>
       <c r="J93" t="n">
-        <v>7.3103</v>
+        <v>6.642</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0319</v>
+        <v>0.0248</v>
       </c>
       <c r="J94" t="n">
-        <v>1.3079</v>
+        <v>1.0168</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.01</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0319</v>
+        <v>0.0248</v>
       </c>
       <c r="J95" t="n">
-        <v>1.3079</v>
+        <v>1.0168</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1721</v>
+        <v>-0.1516</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.0561</v>
+        <v>-6.2156</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.27</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3913</v>
+        <v>0.3286</v>
       </c>
       <c r="J97" t="n">
-        <v>16.0433</v>
+        <v>13.4726</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2447</v>
+        <v>0.1961</v>
       </c>
       <c r="J98" t="n">
-        <v>10.0327</v>
+        <v>8.040100000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2185</v>
+        <v>0.1733</v>
       </c>
       <c r="J99" t="n">
-        <v>8.958500000000001</v>
+        <v>7.1053</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.02</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0467</v>
+        <v>0.0325</v>
       </c>
       <c r="J100" t="n">
-        <v>1.9147</v>
+        <v>1.3325</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.93</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1198</v>
+        <v>-0.1012</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.9118</v>
+        <v>-4.1492</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7448</v>
+        <v>0.7194</v>
       </c>
       <c r="J102" t="n">
-        <v>20.1096</v>
+        <v>19.4238</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.29</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7249</v>
+        <v>0.6986</v>
       </c>
       <c r="J103" t="n">
-        <v>19.5723</v>
+        <v>18.8622</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.28</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7049</v>
+        <v>0.6777</v>
       </c>
       <c r="J104" t="n">
-        <v>19.0323</v>
+        <v>18.2979</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6446</v>
+        <v>0.6153</v>
       </c>
       <c r="J105" t="n">
-        <v>17.4042</v>
+        <v>16.6131</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.12</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3535</v>
+        <v>0.3209</v>
       </c>
       <c r="J106" t="n">
-        <v>9.544499999999999</v>
+        <v>8.664300000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2414</v>
+        <v>0.1969</v>
       </c>
       <c r="J107" t="n">
-        <v>6.5178</v>
+        <v>5.3163</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0477</v>
+        <v>-0.0383</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.2879</v>
+        <v>-1.0341</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1697</v>
+        <v>-0.1516</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.5819</v>
+        <v>-4.0932</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1697</v>
+        <v>-0.1516</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.5819</v>
+        <v>-4.0932</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.452</v>
+        <v>-0.446</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.204</v>
+        <v>-12.042</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9967</v>
+        <v>0.9935</v>
       </c>
       <c r="J112" t="n">
-        <v>29.901</v>
+        <v>29.805</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.17</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4951</v>
+        <v>0.4549</v>
       </c>
       <c r="J113" t="n">
-        <v>14.853</v>
+        <v>13.647</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4718</v>
+        <v>0.4314</v>
       </c>
       <c r="J114" t="n">
-        <v>14.154</v>
+        <v>12.942</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2764</v>
+        <v>-0.2362</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.292</v>
+        <v>-7.086</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.77</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6734</v>
+        <v>-0.6399</v>
       </c>
       <c r="J116" t="n">
-        <v>-20.202</v>
+        <v>-19.197</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.22</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4758</v>
+        <v>0.4176</v>
       </c>
       <c r="J117" t="n">
-        <v>14.274</v>
+        <v>12.528</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.13</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3164</v>
+        <v>0.2645</v>
       </c>
       <c r="J118" t="n">
-        <v>9.492000000000001</v>
+        <v>7.935</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.96</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0704</v>
+        <v>-0.057</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.112</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2691</v>
+        <v>-0.2497</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.073</v>
+        <v>-7.491</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.298</v>
+        <v>-0.2799</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.94</v>
+        <v>-8.397</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.31</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8011</v>
+        <v>0.7746</v>
       </c>
       <c r="J122" t="n">
-        <v>23.2319</v>
+        <v>22.4634</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6306</v>
+        <v>0.5939</v>
       </c>
       <c r="J123" t="n">
-        <v>18.2874</v>
+        <v>17.2231</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.351</v>
+        <v>0.3122</v>
       </c>
       <c r="J124" t="n">
-        <v>10.179</v>
+        <v>9.053800000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2182</v>
+        <v>0.1864</v>
       </c>
       <c r="J125" t="n">
-        <v>6.3278</v>
+        <v>5.4056</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7829</v>
+        <v>-0.7579</v>
       </c>
       <c r="J126" t="n">
-        <v>-22.7041</v>
+        <v>-21.9791</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2953</v>
+        <v>0.245</v>
       </c>
       <c r="J127" t="n">
-        <v>8.563700000000001</v>
+        <v>7.105</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1737</v>
+        <v>0.1357</v>
       </c>
       <c r="J128" t="n">
-        <v>5.0373</v>
+        <v>3.9353</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1336</v>
+        <v>-0.1148</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.8744</v>
+        <v>-3.3292</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1451</v>
+        <v>-0.1257</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.2079</v>
+        <v>-3.6453</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1451</v>
+        <v>-0.1257</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.2079</v>
+        <v>-3.6453</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.41</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9735</v>
+        <v>0.9657</v>
       </c>
       <c r="J132" t="n">
-        <v>29.205</v>
+        <v>28.971</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8593</v>
+        <v>0.8383</v>
       </c>
       <c r="J133" t="n">
-        <v>25.779</v>
+        <v>25.149</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4139</v>
+        <v>0.3782</v>
       </c>
       <c r="J134" t="n">
-        <v>12.417</v>
+        <v>11.346</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0312</v>
+        <v>0.0213</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2323</v>
+        <v>-0.1954</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.969</v>
+        <v>-5.862</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4372</v>
+        <v>0.381</v>
       </c>
       <c r="J137" t="n">
-        <v>13.116</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2069</v>
+        <v>0.1647</v>
       </c>
       <c r="J138" t="n">
-        <v>6.207</v>
+        <v>4.941</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.094</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.82</v>
+        <v>-2.376</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2451</v>
+        <v>-0.2252</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.353</v>
+        <v>-6.756</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.61</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4216</v>
+        <v>-0.4128</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.648</v>
+        <v>-12.384</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4242</v>
+        <v>1.4523</v>
       </c>
       <c r="J142" t="n">
-        <v>32.7566</v>
+        <v>33.4029</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.42</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9751</v>
+        <v>0.9688</v>
       </c>
       <c r="J143" t="n">
-        <v>22.4273</v>
+        <v>22.2824</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9577</v>
+        <v>0.9486</v>
       </c>
       <c r="J144" t="n">
-        <v>22.0271</v>
+        <v>21.8178</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5385</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.3855</v>
+        <v>-11.5345</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.655</v>
+        <v>-0.6242</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.065</v>
+        <v>-14.3566</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.03</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1442</v>
+        <v>0.1143</v>
       </c>
       <c r="J147" t="n">
-        <v>3.3166</v>
+        <v>2.6289</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1529</v>
+        <v>-0.137</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.5167</v>
+        <v>-3.151</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.87</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1639</v>
+        <v>-0.1477</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.7697</v>
+        <v>-3.3971</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2724</v>
+        <v>-0.2547</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.2652</v>
+        <v>-5.8581</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5148</v>
+        <v>-0.516</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.8404</v>
+        <v>-11.868</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.658</v>
+        <v>0.599</v>
       </c>
       <c r="J152" t="n">
-        <v>19.74</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.34</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6429</v>
+        <v>0.5836</v>
       </c>
       <c r="J153" t="n">
-        <v>19.287</v>
+        <v>17.508</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0039</v>
+        <v>-0.0024</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.117</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1856</v>
+        <v>-0.165</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.568</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3063</v>
+        <v>-0.2892</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.189</v>
+        <v>-8.676</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.46</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1025</v>
+        <v>1.119</v>
       </c>
       <c r="J157" t="n">
-        <v>33.075</v>
+        <v>33.57</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1357</v>
+        <v>-0.1078</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.071</v>
+        <v>-3.234</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4693</v>
+        <v>-0.4266</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.079</v>
+        <v>-12.798</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7447</v>
+        <v>-0.7148</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.341</v>
+        <v>-21.444</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.04</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1884</v>
+        <v>0.1573</v>
       </c>
       <c r="J162" t="n">
-        <v>4.3332</v>
+        <v>3.6179</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0585</v>
+        <v>-0.046</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.3455</v>
+        <v>-1.058</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.82</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2106</v>
+        <v>-0.1946</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.8438</v>
+        <v>-4.4758</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2307</v>
+        <v>-0.2146</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.3061</v>
+        <v>-4.9358</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.18</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.772</v>
+        <v>-0.8213</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.756</v>
+        <v>-18.8899</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.67</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2978</v>
+        <v>1.3171</v>
       </c>
       <c r="J167" t="n">
-        <v>29.8494</v>
+        <v>30.2933</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.44</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9897</v>
+        <v>0.9895</v>
       </c>
       <c r="J168" t="n">
-        <v>22.7631</v>
+        <v>22.7585</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8107</v>
+        <v>0.7943</v>
       </c>
       <c r="J169" t="n">
-        <v>18.6461</v>
+        <v>18.2689</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.16</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4338</v>
+        <v>0.4026</v>
       </c>
       <c r="J170" t="n">
-        <v>9.977399999999999</v>
+        <v>9.2598</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.15</v>
       </c>
       <c r="I171" t="n">
-        <v>0.4102</v>
+        <v>0.3787</v>
       </c>
       <c r="J171" t="n">
-        <v>9.4346</v>
+        <v>8.710100000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9272</v>
+        <v>0.9122</v>
       </c>
       <c r="J172" t="n">
-        <v>24.1072</v>
+        <v>23.7172</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.14</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4174</v>
+        <v>0.38</v>
       </c>
       <c r="J173" t="n">
-        <v>10.8524</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.11</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3453</v>
+        <v>0.3094</v>
       </c>
       <c r="J174" t="n">
-        <v>8.9778</v>
+        <v>8.0444</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.08</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2668</v>
+        <v>0.234</v>
       </c>
       <c r="J175" t="n">
-        <v>6.9368</v>
+        <v>6.084</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1237</v>
+        <v>-0.0965</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.2162</v>
+        <v>-2.509</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.11</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2891</v>
+        <v>0.2395</v>
       </c>
       <c r="J177" t="n">
-        <v>7.5166</v>
+        <v>6.227</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.094</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.444</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1063</v>
+        <v>-0.0905</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.7638</v>
+        <v>-2.353</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1839</v>
+        <v>-0.1642</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.7814</v>
+        <v>-4.2692</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.77</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2744</v>
+        <v>-0.2553</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.1344</v>
+        <v>-6.6378</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.75</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4084</v>
+        <v>1.4341</v>
       </c>
       <c r="J182" t="n">
-        <v>32.3932</v>
+        <v>32.9843</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0278</v>
+        <v>1.0317</v>
       </c>
       <c r="J183" t="n">
-        <v>23.6394</v>
+        <v>23.7291</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.34</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8148</v>
+        <v>0.7963</v>
       </c>
       <c r="J184" t="n">
-        <v>18.7404</v>
+        <v>18.3149</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2392</v>
+        <v>0.2089</v>
       </c>
       <c r="J185" t="n">
-        <v>5.5016</v>
+        <v>4.8047</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.9</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3977</v>
+        <v>-0.3595</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.1471</v>
+        <v>-8.2685</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.89</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.137</v>
+        <v>-0.1218</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.151</v>
+        <v>-2.8014</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.242</v>
+        <v>-0.2253</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.566</v>
+        <v>-5.1819</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.79</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.242</v>
+        <v>-0.2253</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.566</v>
+        <v>-5.1819</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3063</v>
+        <v>-0.29</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.0449</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3429</v>
+        <v>-0.3279</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.8867</v>
+        <v>-7.5417</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.68</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8142</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>21.1692</v>
+        <v>19.383</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.39</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4486</v>
       </c>
       <c r="J193" t="n">
-        <v>13.4576</v>
+        <v>11.6636</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1884</v>
+        <v>0.1487</v>
       </c>
       <c r="J194" t="n">
-        <v>4.8984</v>
+        <v>3.8662</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2247</v>
+        <v>-0.205</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.8422</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.74</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3228</v>
+        <v>-0.3077</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.392799999999999</v>
+        <v>-8.0002</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6899</v>
+        <v>0.7386</v>
       </c>
       <c r="J197" t="n">
-        <v>17.9374</v>
+        <v>19.2036</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.96</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0561</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.7836</v>
+        <v>-1.4586</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.185</v>
+        <v>-0.165</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.81</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.71</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3323</v>
+        <v>-0.316</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.639799999999999</v>
+        <v>-8.215999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.67</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.369</v>
+        <v>-0.3554</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.593999999999999</v>
+        <v>-9.240399999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.28</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5535</v>
+        <v>0.4937</v>
       </c>
       <c r="J202" t="n">
-        <v>23.247</v>
+        <v>20.7354</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.27</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5376</v>
+        <v>0.4779</v>
       </c>
       <c r="J203" t="n">
-        <v>22.5792</v>
+        <v>20.0718</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.7758</v>
+        <v>-3.0828</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.87</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1844</v>
+        <v>-0.1638</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.7448</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.87</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1844</v>
+        <v>-0.1638</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.7448</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.929</v>
+        <v>0.9166</v>
       </c>
       <c r="J207" t="n">
-        <v>39.018</v>
+        <v>38.4972</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3648</v>
+        <v>0.3227</v>
       </c>
       <c r="J208" t="n">
-        <v>15.3216</v>
+        <v>13.5534</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.08</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2846</v>
+        <v>0.2453</v>
       </c>
       <c r="J209" t="n">
-        <v>11.9532</v>
+        <v>10.3026</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.52</v>
+        <v>-0.4784</v>
       </c>
       <c r="J210" t="n">
-        <v>-21.84</v>
+        <v>-20.0928</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8333</v>
+        <v>-0.8112</v>
       </c>
       <c r="J211" t="n">
-        <v>-34.9986</v>
+        <v>-34.0704</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.18</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4138</v>
+        <v>0.3576</v>
       </c>
       <c r="J212" t="n">
-        <v>12.414</v>
+        <v>10.728</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0513</v>
+        <v>0.0344</v>
       </c>
       <c r="J213" t="n">
-        <v>1.539</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0825</v>
+        <v>-0.0683</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.475</v>
+        <v>-2.049</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1962</v>
+        <v>-0.176</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.886</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.72</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3238</v>
+        <v>-0.307</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.714</v>
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8605</v>
+        <v>0.8397</v>
       </c>
       <c r="J217" t="n">
-        <v>25.815</v>
+        <v>25.191</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5316</v>
+        <v>0.4905</v>
       </c>
       <c r="J218" t="n">
-        <v>15.948</v>
+        <v>14.715</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0959</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>2.877</v>
+        <v>2.244</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4998</v>
+        <v>-0.4576</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.994</v>
+        <v>-13.728</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6171</v>
+        <v>-0.5794</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.513</v>
+        <v>-17.382</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2979</v>
+        <v>0.2474</v>
       </c>
       <c r="J222" t="n">
-        <v>8.341200000000001</v>
+        <v>6.9272</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.08</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2186</v>
+        <v>0.1751</v>
       </c>
       <c r="J223" t="n">
-        <v>6.1208</v>
+        <v>4.9028</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0235</v>
+        <v>-0.0173</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.658</v>
+        <v>-0.4844</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0837</v>
+        <v>-0.0688</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.3436</v>
+        <v>-1.9264</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3538</v>
+        <v>-0.3392</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.9064</v>
+        <v>-9.4976</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>1.0944</v>
+        <v>1.1057</v>
       </c>
       <c r="J227" t="n">
-        <v>30.6432</v>
+        <v>30.9596</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.24</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6435</v>
+        <v>0.6083</v>
       </c>
       <c r="J228" t="n">
-        <v>18.018</v>
+        <v>17.0324</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1509</v>
+        <v>0.1258</v>
       </c>
       <c r="J229" t="n">
-        <v>4.2252</v>
+        <v>3.5224</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1916</v>
+        <v>-0.1569</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.3648</v>
+        <v>-4.3932</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3663</v>
+        <v>-0.324</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.2564</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.78</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2367</v>
+        <v>-0.2224</v>
       </c>
       <c r="J232" t="n">
-        <v>-5.2074</v>
+        <v>-4.8928</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.75</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2668</v>
+        <v>-0.2533</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.8696</v>
+        <v>-5.5726</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.7</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3142</v>
+        <v>-0.3019</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.9124</v>
+        <v>-6.6418</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3233</v>
+        <v>-0.3111</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.1126</v>
+        <v>-6.8442</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.41</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5683</v>
+        <v>-0.5755</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.5026</v>
+        <v>-12.661</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>1.621</v>
+        <v>1.6617</v>
       </c>
       <c r="J237" t="n">
-        <v>35.662</v>
+        <v>36.5574</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.66</v>
       </c>
       <c r="I238" t="n">
-        <v>1.262</v>
+        <v>1.2825</v>
       </c>
       <c r="J238" t="n">
-        <v>27.764</v>
+        <v>28.215</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.4</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9055</v>
+        <v>0.9022</v>
       </c>
       <c r="J239" t="n">
-        <v>19.921</v>
+        <v>19.8484</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.27</v>
       </c>
       <c r="I240" t="n">
-        <v>0.652</v>
+        <v>0.6308</v>
       </c>
       <c r="J240" t="n">
-        <v>14.344</v>
+        <v>13.8776</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.23</v>
       </c>
       <c r="I241" t="n">
-        <v>0.5679</v>
+        <v>0.542</v>
       </c>
       <c r="J241" t="n">
-        <v>12.4938</v>
+        <v>11.924</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4487</v>
+        <v>0.3938</v>
       </c>
       <c r="J242" t="n">
-        <v>10.3201</v>
+        <v>9.057399999999999</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0625</v>
+        <v>0.0438</v>
       </c>
       <c r="J243" t="n">
-        <v>1.4375</v>
+        <v>1.0074</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1386</v>
+        <v>-0.1215</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.1878</v>
+        <v>-2.7945</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.7</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3368</v>
+        <v>-0.3207</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.7464</v>
+        <v>-7.3761</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.63</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4003</v>
+        <v>-0.3891</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.206899999999999</v>
+        <v>-8.949299999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.47</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0462</v>
+        <v>1.0523</v>
       </c>
       <c r="J247" t="n">
-        <v>24.0626</v>
+        <v>24.2029</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.39</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9132</v>
+        <v>0.9002</v>
       </c>
       <c r="J248" t="n">
-        <v>21.0036</v>
+        <v>20.7046</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.36</v>
       </c>
       <c r="I249" t="n">
-        <v>0.8563</v>
+        <v>0.8391</v>
       </c>
       <c r="J249" t="n">
-        <v>19.6949</v>
+        <v>19.2993</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.25</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6412</v>
+        <v>0.6136</v>
       </c>
       <c r="J250" t="n">
-        <v>14.7476</v>
+        <v>14.1128</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.95</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2516</v>
+        <v>-0.2165</v>
       </c>
       <c r="J251" t="n">
-        <v>-5.7868</v>
+        <v>-4.9795</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>2.08</v>
       </c>
       <c r="I252" t="n">
-        <v>1.7338</v>
+        <v>1.7846</v>
       </c>
       <c r="J252" t="n">
-        <v>32.9422</v>
+        <v>33.9074</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.79</v>
       </c>
       <c r="I253" t="n">
-        <v>1.4022</v>
+        <v>1.4313</v>
       </c>
       <c r="J253" t="n">
-        <v>26.6418</v>
+        <v>27.1947</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.55</v>
       </c>
       <c r="I254" t="n">
-        <v>1.116</v>
+        <v>1.1384</v>
       </c>
       <c r="J254" t="n">
-        <v>21.204</v>
+        <v>21.6296</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.43</v>
       </c>
       <c r="I255" t="n">
-        <v>0.9423</v>
+        <v>0.9468</v>
       </c>
       <c r="J255" t="n">
-        <v>17.9037</v>
+        <v>17.9892</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.36</v>
       </c>
       <c r="I256" t="n">
-        <v>0.8123</v>
+        <v>0.804</v>
       </c>
       <c r="J256" t="n">
-        <v>15.4337</v>
+        <v>15.276</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.68</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2901</v>
+        <v>-0.2757</v>
       </c>
       <c r="J257" t="n">
-        <v>-5.5119</v>
+        <v>-5.2383</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.54</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.4288</v>
+        <v>-0.4271</v>
       </c>
       <c r="J258" t="n">
-        <v>-8.1472</v>
+        <v>-8.1149</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.52</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4468</v>
+        <v>-0.4459</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.4892</v>
+        <v>-8.472099999999999</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.41</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5405</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.2695</v>
+        <v>-10.3341</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.28</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6586</v>
+        <v>-0.6784</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.5134</v>
+        <v>-12.8896</v>
       </c>
     </row>
   </sheetData>
